--- a/Versão5/GIS/Ontologia_OSM.xlsx
+++ b/Versão5/GIS/Ontologia_OSM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2927FA0-0469-4835-B295-8B23BA9371AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7F91D4-770A-4D90-BEAC-C11AC5F0C801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="681" activeTab="4" xr2:uid="{EADD6BF3-7ABC-4ACF-B5B1-0F5DE0265229}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="681" activeTab="1" xr2:uid="{EADD6BF3-7ABC-4ACF-B5B1-0F5DE0265229}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="16" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="220">
   <si>
     <t>Organização</t>
   </si>
@@ -362,9 +362,6 @@
     <t>Interop</t>
   </si>
   <si>
-    <t>Elemento KML</t>
-  </si>
-  <si>
     <t>Projeto</t>
   </si>
   <si>
@@ -375,12 +372,6 @@
   </si>
   <si>
     <t>Macros</t>
-  </si>
-  <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
   </si>
   <si>
     <t>OSM</t>
@@ -615,9 +606,6 @@
     <t>Clase de esquema OSM para infraestructuras. Es una estación de bombeo o bombeo de aguas residuales.</t>
   </si>
   <si>
-    <t>Aplicación Revit</t>
-  </si>
-  <si>
     <t>OSM schema class for infrastructure. It is a power-generator.</t>
   </si>
   <si>
@@ -684,7 +672,70 @@
     <t>OSM schematic class for infrastructure. It is a sewage pumping or pumping station.</t>
   </si>
   <si>
-    <t>Revit App</t>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -783,7 +834,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -865,12 +916,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE79D"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1102,28 +1147,22 @@
     <xf numFmtId="0" fontId="4" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1136,15 +1175,15 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1152,7 +1191,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1170,12 +1209,12 @@
     <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1191,13 +1230,10 @@
     <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1215,12 +1251,12 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1245,15 +1281,24 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="25">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1443,6 +1488,16 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1851,7 +1906,7 @@
   <sheetFormatPr defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
-    <col min="2" max="2" width="65.33203125" style="29" customWidth="1"/>
+    <col min="2" max="2" width="65.33203125" style="27" customWidth="1"/>
     <col min="3" max="3" width="4.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1882,7 +1937,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>11</v>
@@ -2026,8 +2081,8 @@
       <c r="A16" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B16" s="47" t="s">
-        <v>106</v>
+      <c r="B16" s="44" t="s">
+        <v>103</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>11</v>
@@ -2038,7 +2093,7 @@
         <v>29</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>11</v>
@@ -2050,7 +2105,7 @@
       </c>
       <c r="B18" s="7">
         <f ca="1">NOW()</f>
-        <v>46268.329303240738</v>
+        <v>46268.697977662036</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>11</v>
@@ -2094,7 +2149,7 @@
         <v>35</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>11</v>
@@ -2134,7 +2189,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B21B10B-C8BF-4318-B9A8-B9240E89A4C8}">
-  <dimension ref="A1:AD24"/>
+  <dimension ref="A1:AD28"/>
   <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
@@ -2161,41 +2216,41 @@
     <col min="27" max="27" width="20" customWidth="1"/>
     <col min="28" max="28" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="42">
+      <c r="A1" s="40">
         <v>1</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="G1" s="35" t="s">
+      <c r="F1" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="G1" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="35" t="s">
+      <c r="H1" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="35" t="s">
+      <c r="I1" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="35" t="s">
+      <c r="J1" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="33" t="s">
         <v>48</v>
       </c>
       <c r="L1" s="9" t="s">
@@ -2234,2350 +2289,2753 @@
       <c r="W1" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="X1" s="34" t="s">
+      <c r="X1" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="Y1" s="33" t="s">
+      <c r="Y1" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="Z1" s="33" t="s">
+      <c r="Z1" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="AA1" s="33" t="s">
+      <c r="AA1" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="AB1" s="33" t="s">
+      <c r="AB1" s="31" t="s">
         <v>92</v>
       </c>
       <c r="AC1" s="9" t="s">
         <v>62</v>
       </c>
       <c r="AD1" s="9" t="s">
-        <v>95</v>
+        <v>219</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="31">
-        <v>2</v>
-      </c>
-      <c r="B2" s="11" t="s">
+      <c r="A2" s="29">
+        <v>2</v>
+      </c>
+      <c r="B2" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="E2" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F2" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="G2" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I2" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J2" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K2" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L2" s="13" t="str">
+      <c r="E2" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L2" s="11" t="str">
         <f t="shared" ref="L2:L22" si="0">CONCATENATE("", C2)</f>
         <v>Interoperabilidade</v>
       </c>
-      <c r="M2" s="13" t="str">
+      <c r="M2" s="11" t="str">
         <f t="shared" ref="M2:M22" si="1">CONCATENATE("", D2)</f>
         <v>Esquemas</v>
       </c>
-      <c r="N2" s="13" t="str">
+      <c r="N2" s="11" t="str">
         <f t="shared" ref="N2:N22" si="2">CONCATENATE("", E2)</f>
         <v>OSM</v>
       </c>
-      <c r="O2" s="13" t="str">
+      <c r="O2" s="11" t="str">
         <f t="shared" ref="O2:O22" si="3">CONCATENATE("", F2)</f>
         <v>Energia.Gerador</v>
       </c>
-      <c r="P2" s="37" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q2" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="R2" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="S2" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="T2" s="14" t="str">
+      <c r="P2" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T2" s="12" t="str">
         <f t="shared" ref="T2:T22" si="4">SUBSTITUTE(C2, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
-      <c r="U2" s="14" t="str">
+      <c r="U2" s="12" t="str">
         <f t="shared" ref="U2:U22" si="5">SUBSTITUTE(D2, "_", " ")</f>
         <v>Esquemas</v>
       </c>
-      <c r="V2" s="14" t="str">
+      <c r="V2" s="12" t="str">
         <f t="shared" ref="V2:V22" si="6">SUBSTITUTE(F2, "_", " ")</f>
         <v>Energia.Gerador</v>
       </c>
-      <c r="W2" s="14" t="s">
+      <c r="W2" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="X2" s="30" t="str">
+      <c r="X2" s="28" t="str">
         <f>CONCATENATE("Key-OSMI-",A2)</f>
         <v>Key-OSMI-2</v>
       </c>
-      <c r="Y2" s="61" t="s">
-        <v>131</v>
-      </c>
-      <c r="Z2" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA2" s="61" t="s">
-        <v>132</v>
-      </c>
-      <c r="AB2" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC2" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD2" s="14" t="s">
+      <c r="Y2" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z2" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA2" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD2" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="31">
+      <c r="A3" s="29">
         <v>3</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F3" s="36" t="s">
-        <v>111</v>
-      </c>
-      <c r="G3" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J3" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K3" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L3" s="13" t="str">
+      <c r="E3" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="G3" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K3" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L3" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="M3" s="13" t="str">
+      <c r="M3" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
-      <c r="N3" s="13" t="str">
+      <c r="N3" s="11" t="str">
         <f t="shared" si="2"/>
         <v>OSM</v>
       </c>
-      <c r="O3" s="13" t="str">
+      <c r="O3" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Energia.Usina</v>
       </c>
-      <c r="P3" s="37" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q3" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="R3" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="S3" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="T3" s="14" t="str">
+      <c r="P3" s="35" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q3" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="R3" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="S3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T3" s="12" t="str">
         <f t="shared" si="4"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="U3" s="14" t="str">
+      <c r="U3" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Esquemas</v>
       </c>
-      <c r="V3" s="14" t="str">
+      <c r="V3" s="12" t="str">
         <f t="shared" si="6"/>
         <v>Energia.Usina</v>
       </c>
-      <c r="W3" s="14" t="s">
+      <c r="W3" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="X3" s="30" t="str">
-        <f t="shared" ref="X3:X24" si="7">CONCATENATE("Key-OSMI-",A3)</f>
+      <c r="X3" s="28" t="str">
+        <f t="shared" ref="X3:X22" si="7">CONCATENATE("Key-OSMI-",A3)</f>
         <v>Key-OSMI-3</v>
       </c>
-      <c r="Y3" s="61" t="s">
-        <v>131</v>
-      </c>
-      <c r="Z3" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA3" s="61" t="s">
-        <v>132</v>
-      </c>
-      <c r="AB3" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC3" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD3" s="14" t="s">
+      <c r="Y3" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z3" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA3" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD3" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="31">
+      <c r="A4" s="29">
         <v>4</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="E4" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F4" s="36" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H4" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I4" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J4" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K4" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L4" s="13" t="str">
+      <c r="E4" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="F4" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J4" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K4" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L4" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="M4" s="13" t="str">
+      <c r="M4" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
-      <c r="N4" s="13" t="str">
+      <c r="N4" s="11" t="str">
         <f t="shared" si="2"/>
         <v>OSM</v>
       </c>
-      <c r="O4" s="13" t="str">
+      <c r="O4" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Energia.Linha</v>
       </c>
-      <c r="P4" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q4" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="R4" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="S4" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="T4" s="14" t="str">
+      <c r="P4" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q4" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="R4" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="S4" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T4" s="12" t="str">
         <f t="shared" si="4"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="U4" s="14" t="str">
+      <c r="U4" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Esquemas</v>
       </c>
-      <c r="V4" s="14" t="str">
+      <c r="V4" s="12" t="str">
         <f t="shared" si="6"/>
         <v>Energia.Linha</v>
       </c>
-      <c r="W4" s="14" t="s">
+      <c r="W4" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="X4" s="30" t="str">
+      <c r="X4" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-4</v>
       </c>
-      <c r="Y4" s="61" t="s">
-        <v>131</v>
-      </c>
-      <c r="Z4" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA4" s="61" t="s">
-        <v>132</v>
-      </c>
-      <c r="AB4" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC4" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD4" s="14" t="s">
+      <c r="Y4" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z4" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA4" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB4" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC4" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD4" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="31">
+      <c r="A5" s="29">
         <v>5</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F5" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="G5" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H5" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I5" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J5" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K5" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L5" s="13" t="str">
+      <c r="E5" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J5" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K5" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L5" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="M5" s="13" t="str">
+      <c r="M5" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
-      <c r="N5" s="13" t="str">
+      <c r="N5" s="11" t="str">
         <f t="shared" si="2"/>
         <v>OSM</v>
       </c>
-      <c r="O5" s="13" t="str">
+      <c r="O5" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Energia.Subestação</v>
       </c>
-      <c r="P5" s="37" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q5" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="R5" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="S5" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="T5" s="14" t="str">
+      <c r="P5" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="R5" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="S5" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T5" s="12" t="str">
         <f t="shared" si="4"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="U5" s="14" t="str">
+      <c r="U5" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Esquemas</v>
       </c>
-      <c r="V5" s="14" t="str">
+      <c r="V5" s="12" t="str">
         <f t="shared" si="6"/>
         <v>Energia.Subestação</v>
       </c>
-      <c r="W5" s="14" t="s">
+      <c r="W5" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="X5" s="30" t="str">
+      <c r="X5" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-5</v>
       </c>
-      <c r="Y5" s="61" t="s">
-        <v>131</v>
-      </c>
-      <c r="Z5" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA5" s="61" t="s">
-        <v>132</v>
-      </c>
-      <c r="AB5" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC5" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD5" s="14" t="s">
+      <c r="Y5" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z5" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA5" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB5" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC5" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD5" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="31">
+      <c r="A6" s="29">
         <v>6</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="E6" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F6" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="G6" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H6" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I6" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J6" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K6" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L6" s="13" t="str">
+      <c r="E6" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="G6" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H6" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I6" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J6" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K6" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L6" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="M6" s="13" t="str">
+      <c r="M6" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
-      <c r="N6" s="13" t="str">
+      <c r="N6" s="11" t="str">
         <f t="shared" si="2"/>
         <v>OSM</v>
       </c>
-      <c r="O6" s="13" t="str">
+      <c r="O6" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Energia.Transformador</v>
       </c>
-      <c r="P6" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q6" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="R6" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="S6" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="T6" s="14" t="str">
+      <c r="P6" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="R6" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="S6" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T6" s="12" t="str">
         <f t="shared" si="4"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="U6" s="14" t="str">
+      <c r="U6" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Esquemas</v>
       </c>
-      <c r="V6" s="14" t="str">
+      <c r="V6" s="12" t="str">
         <f t="shared" si="6"/>
         <v>Energia.Transformador</v>
       </c>
-      <c r="W6" s="14" t="s">
+      <c r="W6" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="X6" s="30" t="str">
+      <c r="X6" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-6</v>
       </c>
-      <c r="Y6" s="61" t="s">
-        <v>131</v>
-      </c>
-      <c r="Z6" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA6" s="61" t="s">
-        <v>132</v>
-      </c>
-      <c r="AB6" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC6" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD6" s="14" t="s">
+      <c r="Y6" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z6" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA6" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB6" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC6" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD6" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="31">
+      <c r="A7" s="29">
         <v>7</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="E7" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F7" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="G7" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H7" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I7" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J7" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K7" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L7" s="13" t="str">
+      <c r="E7" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H7" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I7" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J7" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K7" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L7" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="M7" s="13" t="str">
+      <c r="M7" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
-      <c r="N7" s="13" t="str">
+      <c r="N7" s="11" t="str">
         <f t="shared" si="2"/>
         <v>OSM</v>
       </c>
-      <c r="O7" s="13" t="str">
+      <c r="O7" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Energia.Interruptor</v>
       </c>
-      <c r="P7" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q7" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="R7" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="S7" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="T7" s="14" t="str">
+      <c r="P7" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q7" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="R7" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="S7" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T7" s="12" t="str">
         <f t="shared" si="4"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="U7" s="14" t="str">
+      <c r="U7" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Esquemas</v>
       </c>
-      <c r="V7" s="14" t="str">
+      <c r="V7" s="12" t="str">
         <f t="shared" si="6"/>
         <v>Energia.Interruptor</v>
       </c>
-      <c r="W7" s="14" t="s">
+      <c r="W7" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="X7" s="30" t="str">
+      <c r="X7" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-7</v>
       </c>
-      <c r="Y7" s="61" t="s">
-        <v>131</v>
-      </c>
-      <c r="Z7" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA7" s="61" t="s">
-        <v>132</v>
-      </c>
-      <c r="AB7" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC7" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD7" s="14" t="s">
+      <c r="Y7" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z7" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA7" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB7" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC7" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD7" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="31">
+      <c r="A8" s="29">
         <v>8</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F8" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="G8" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H8" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I8" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J8" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K8" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L8" s="13" t="str">
+      <c r="E8" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H8" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I8" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J8" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K8" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L8" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="M8" s="13" t="str">
+      <c r="M8" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
-      <c r="N8" s="13" t="str">
+      <c r="N8" s="11" t="str">
         <f t="shared" si="2"/>
         <v>OSM</v>
       </c>
-      <c r="O8" s="13" t="str">
+      <c r="O8" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Energia.Compensador</v>
       </c>
-      <c r="P8" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q8" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="R8" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="S8" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="T8" s="14" t="str">
+      <c r="P8" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q8" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="R8" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="S8" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T8" s="12" t="str">
         <f t="shared" si="4"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="U8" s="14" t="str">
+      <c r="U8" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Esquemas</v>
       </c>
-      <c r="V8" s="14" t="str">
+      <c r="V8" s="12" t="str">
         <f t="shared" si="6"/>
         <v>Energia.Compensador</v>
       </c>
-      <c r="W8" s="14" t="s">
+      <c r="W8" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="X8" s="30" t="str">
+      <c r="X8" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-8</v>
       </c>
-      <c r="Y8" s="61" t="s">
-        <v>131</v>
-      </c>
-      <c r="Z8" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA8" s="61" t="s">
-        <v>132</v>
-      </c>
-      <c r="AB8" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC8" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD8" s="14" t="s">
+      <c r="Y8" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z8" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA8" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB8" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC8" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD8" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="31">
+      <c r="A9" s="29">
         <v>9</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="E9" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F9" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="G9" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H9" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I9" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J9" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K9" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L9" s="13" t="str">
+      <c r="E9" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H9" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I9" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L9" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="M9" s="13" t="str">
+      <c r="M9" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
-      <c r="N9" s="13" t="str">
+      <c r="N9" s="11" t="str">
         <f t="shared" si="2"/>
         <v>OSM</v>
       </c>
-      <c r="O9" s="13" t="str">
+      <c r="O9" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Energia.Torre</v>
       </c>
-      <c r="P9" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q9" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="R9" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="S9" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="T9" s="14" t="str">
+      <c r="P9" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q9" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="R9" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="S9" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T9" s="12" t="str">
         <f t="shared" si="4"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="U9" s="14" t="str">
+      <c r="U9" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Esquemas</v>
       </c>
-      <c r="V9" s="14" t="str">
+      <c r="V9" s="12" t="str">
         <f t="shared" si="6"/>
         <v>Energia.Torre</v>
       </c>
-      <c r="W9" s="14" t="s">
+      <c r="W9" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="X9" s="30" t="str">
+      <c r="X9" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-9</v>
       </c>
-      <c r="Y9" s="61" t="s">
-        <v>131</v>
-      </c>
-      <c r="Z9" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA9" s="61" t="s">
-        <v>132</v>
-      </c>
-      <c r="AB9" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC9" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD9" s="14" t="s">
+      <c r="Y9" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z9" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA9" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB9" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC9" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD9" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="31">
+      <c r="A10" s="29">
         <v>10</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="E10" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F10" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="G10" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H10" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I10" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J10" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K10" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L10" s="13" t="str">
+      <c r="E10" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="G10" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H10" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I10" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J10" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K10" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L10" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="M10" s="13" t="str">
+      <c r="M10" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
-      <c r="N10" s="13" t="str">
+      <c r="N10" s="11" t="str">
         <f t="shared" si="2"/>
         <v>OSM</v>
       </c>
-      <c r="O10" s="13" t="str">
+      <c r="O10" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Telecom.Edifício</v>
       </c>
-      <c r="P10" s="37" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q10" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="R10" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="S10" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="T10" s="14" t="str">
+      <c r="P10" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q10" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="R10" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="S10" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T10" s="12" t="str">
         <f t="shared" si="4"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="U10" s="14" t="str">
+      <c r="U10" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Esquemas</v>
       </c>
-      <c r="V10" s="14" t="str">
+      <c r="V10" s="12" t="str">
         <f t="shared" si="6"/>
         <v>Telecom.Edifício</v>
       </c>
-      <c r="W10" s="14" t="s">
+      <c r="W10" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="X10" s="30" t="str">
+      <c r="X10" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-10</v>
       </c>
-      <c r="Y10" s="61" t="s">
-        <v>131</v>
-      </c>
-      <c r="Z10" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA10" s="61" t="s">
-        <v>132</v>
-      </c>
-      <c r="AB10" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC10" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD10" s="14" t="s">
+      <c r="Y10" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z10" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA10" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB10" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC10" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD10" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="31">
+      <c r="A11" s="29">
         <v>11</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="E11" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F11" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="G11" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H11" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I11" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J11" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K11" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L11" s="13" t="str">
+      <c r="E11" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="F11" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="G11" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H11" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I11" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J11" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K11" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L11" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="M11" s="13" t="str">
+      <c r="M11" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
-      <c r="N11" s="13" t="str">
+      <c r="N11" s="11" t="str">
         <f t="shared" si="2"/>
         <v>OSM</v>
       </c>
-      <c r="O11" s="13" t="str">
+      <c r="O11" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Telecom.Cabo</v>
       </c>
-      <c r="P11" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q11" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="R11" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="S11" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="T11" s="14" t="str">
+      <c r="P11" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q11" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="R11" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="S11" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T11" s="12" t="str">
         <f t="shared" si="4"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="U11" s="14" t="str">
+      <c r="U11" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Esquemas</v>
       </c>
-      <c r="V11" s="14" t="str">
+      <c r="V11" s="12" t="str">
         <f t="shared" si="6"/>
         <v>Telecom.Cabo</v>
       </c>
-      <c r="W11" s="14" t="s">
+      <c r="W11" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="X11" s="30" t="str">
+      <c r="X11" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-11</v>
       </c>
-      <c r="Y11" s="61" t="s">
-        <v>131</v>
-      </c>
-      <c r="Z11" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA11" s="61" t="s">
-        <v>132</v>
-      </c>
-      <c r="AB11" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC11" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD11" s="14" t="s">
+      <c r="Y11" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z11" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA11" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB11" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC11" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD11" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="31">
+      <c r="A12" s="29">
         <v>12</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="E12" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F12" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="G12" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H12" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I12" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J12" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K12" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L12" s="13" t="str">
+      <c r="E12" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="F12" s="34" t="s">
+        <v>117</v>
+      </c>
+      <c r="G12" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H12" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I12" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J12" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K12" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L12" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="M12" s="13" t="str">
+      <c r="M12" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
-      <c r="N12" s="13" t="str">
+      <c r="N12" s="11" t="str">
         <f t="shared" si="2"/>
         <v>OSM</v>
       </c>
-      <c r="O12" s="13" t="str">
+      <c r="O12" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Telecom.Mastro</v>
       </c>
-      <c r="P12" s="37" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q12" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="R12" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="S12" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="T12" s="14" t="str">
+      <c r="P12" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q12" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="R12" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="S12" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T12" s="12" t="str">
         <f t="shared" si="4"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="U12" s="14" t="str">
+      <c r="U12" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Esquemas</v>
       </c>
-      <c r="V12" s="14" t="str">
+      <c r="V12" s="12" t="str">
         <f t="shared" si="6"/>
         <v>Telecom.Mastro</v>
       </c>
-      <c r="W12" s="14" t="s">
+      <c r="W12" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="X12" s="30" t="str">
+      <c r="X12" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-12</v>
       </c>
-      <c r="Y12" s="61" t="s">
-        <v>131</v>
-      </c>
-      <c r="Z12" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA12" s="61" t="s">
-        <v>132</v>
-      </c>
-      <c r="AB12" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC12" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD12" s="14" t="s">
+      <c r="Y12" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z12" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA12" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB12" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC12" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD12" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="31">
+      <c r="A13" s="29">
         <v>13</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="E13" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F13" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="G13" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H13" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I13" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J13" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K13" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L13" s="13" t="str">
+      <c r="E13" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="F13" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="G13" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H13" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I13" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J13" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K13" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L13" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="M13" s="13" t="str">
+      <c r="M13" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
-      <c r="N13" s="13" t="str">
+      <c r="N13" s="11" t="str">
         <f t="shared" si="2"/>
         <v>OSM</v>
       </c>
-      <c r="O13" s="13" t="str">
+      <c r="O13" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Oleoduto</v>
       </c>
-      <c r="P13" s="37" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q13" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="R13" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="S13" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="T13" s="14" t="str">
+      <c r="P13" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q13" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="R13" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="S13" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T13" s="12" t="str">
         <f t="shared" si="4"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="U13" s="14" t="str">
+      <c r="U13" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Esquemas</v>
       </c>
-      <c r="V13" s="14" t="str">
+      <c r="V13" s="12" t="str">
         <f t="shared" si="6"/>
         <v>Oleoduto</v>
       </c>
-      <c r="W13" s="14" t="s">
+      <c r="W13" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="X13" s="30" t="str">
+      <c r="X13" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-13</v>
       </c>
-      <c r="Y13" s="61" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z13" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA13" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="AB13" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC13" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD13" s="14" t="s">
+      <c r="Y13" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z13" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA13" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="AB13" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC13" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD13" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="31">
+      <c r="A14" s="29">
         <v>14</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F14" s="36" t="s">
-        <v>121</v>
-      </c>
-      <c r="G14" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H14" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I14" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J14" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K14" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L14" s="13" t="str">
+      <c r="E14" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>118</v>
+      </c>
+      <c r="G14" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H14" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I14" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J14" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K14" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L14" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="M14" s="13" t="str">
+      <c r="M14" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
-      <c r="N14" s="13" t="str">
+      <c r="N14" s="11" t="str">
         <f t="shared" si="2"/>
         <v>OSM</v>
       </c>
-      <c r="O14" s="13" t="str">
+      <c r="O14" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Oleoduto.Parte.de.Tubulação</v>
       </c>
-      <c r="P14" s="37" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q14" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="R14" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="S14" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="T14" s="14" t="str">
+      <c r="P14" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q14" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="R14" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="S14" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T14" s="12" t="str">
         <f t="shared" si="4"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="U14" s="14" t="str">
+      <c r="U14" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Esquemas</v>
       </c>
-      <c r="V14" s="14" t="str">
+      <c r="V14" s="12" t="str">
         <f t="shared" si="6"/>
         <v>Oleoduto.Parte.de.Tubulação</v>
       </c>
-      <c r="W14" s="14" t="s">
+      <c r="W14" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="X14" s="30" t="str">
+      <c r="X14" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-14</v>
       </c>
-      <c r="Y14" s="61" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z14" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA14" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="AB14" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC14" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD14" s="14" t="s">
+      <c r="Y14" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z14" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA14" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="AB14" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC14" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD14" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="31">
+      <c r="A15" s="29">
         <v>15</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="E15" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F15" s="36" t="s">
-        <v>123</v>
-      </c>
-      <c r="G15" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H15" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I15" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J15" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K15" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L15" s="13" t="str">
+      <c r="E15" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="F15" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="G15" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H15" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I15" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J15" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K15" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L15" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="M15" s="13" t="str">
+      <c r="M15" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
-      <c r="N15" s="13" t="str">
+      <c r="N15" s="11" t="str">
         <f t="shared" si="2"/>
         <v>OSM</v>
       </c>
-      <c r="O15" s="13" t="str">
+      <c r="O15" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Petróleo.Campo</v>
       </c>
-      <c r="P15" s="37" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q15" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="R15" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="S15" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="T15" s="14" t="str">
+      <c r="P15" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q15" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="R15" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="S15" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T15" s="12" t="str">
         <f t="shared" si="4"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="U15" s="14" t="str">
+      <c r="U15" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Esquemas</v>
       </c>
-      <c r="V15" s="14" t="str">
+      <c r="V15" s="12" t="str">
         <f t="shared" si="6"/>
         <v>Petróleo.Campo</v>
       </c>
-      <c r="W15" s="14" t="s">
+      <c r="W15" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="X15" s="30" t="str">
+      <c r="X15" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-15</v>
       </c>
-      <c r="Y15" s="61" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z15" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA15" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="AB15" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC15" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD15" s="14" t="s">
+      <c r="Y15" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z15" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA15" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="AB15" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC15" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD15" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="31">
+      <c r="A16" s="29">
         <v>16</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="E16" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F16" s="36" t="s">
-        <v>122</v>
-      </c>
-      <c r="G16" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H16" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I16" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J16" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K16" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L16" s="13" t="str">
+      <c r="E16" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="F16" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="G16" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H16" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I16" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J16" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K16" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L16" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="M16" s="13" t="str">
+      <c r="M16" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
-      <c r="N16" s="13" t="str">
+      <c r="N16" s="11" t="str">
         <f t="shared" si="2"/>
         <v>OSM</v>
       </c>
-      <c r="O16" s="13" t="str">
+      <c r="O16" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Petróleo.Poço</v>
       </c>
-      <c r="P16" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q16" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="R16" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="S16" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="T16" s="14" t="str">
+      <c r="P16" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q16" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="R16" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="S16" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T16" s="12" t="str">
         <f t="shared" si="4"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="U16" s="14" t="str">
+      <c r="U16" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Esquemas</v>
       </c>
-      <c r="V16" s="14" t="str">
+      <c r="V16" s="12" t="str">
         <f t="shared" si="6"/>
         <v>Petróleo.Poço</v>
       </c>
-      <c r="W16" s="14" t="s">
+      <c r="W16" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="X16" s="30" t="str">
+      <c r="X16" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-16</v>
       </c>
-      <c r="Y16" s="61" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z16" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA16" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="AB16" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC16" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD16" s="14" t="s">
+      <c r="Y16" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z16" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA16" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="AB16" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC16" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD16" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="31">
+      <c r="A17" s="29">
         <v>17</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="E17" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F17" s="36" t="s">
-        <v>124</v>
-      </c>
-      <c r="G17" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H17" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I17" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J17" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K17" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L17" s="13" t="str">
+      <c r="E17" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="F17" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="G17" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H17" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I17" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J17" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K17" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L17" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="M17" s="13" t="str">
+      <c r="M17" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
-      <c r="N17" s="13" t="str">
+      <c r="N17" s="11" t="str">
         <f t="shared" si="2"/>
         <v>OSM</v>
       </c>
-      <c r="O17" s="13" t="str">
+      <c r="O17" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Água.Estação.de.Tratamento</v>
       </c>
-      <c r="P17" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q17" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="R17" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="S17" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="T17" s="14" t="str">
+      <c r="P17" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q17" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="R17" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="S17" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T17" s="12" t="str">
         <f t="shared" si="4"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="U17" s="14" t="str">
+      <c r="U17" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Esquemas</v>
       </c>
-      <c r="V17" s="14" t="str">
+      <c r="V17" s="12" t="str">
         <f t="shared" si="6"/>
         <v>Água.Estação.de.Tratamento</v>
       </c>
-      <c r="W17" s="14" t="s">
+      <c r="W17" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="X17" s="30" t="str">
+      <c r="X17" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-17</v>
       </c>
-      <c r="Y17" s="61" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z17" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA17" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="AB17" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC17" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD17" s="14" t="s">
+      <c r="Y17" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z17" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA17" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="AB17" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC17" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD17" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="31">
+      <c r="A18" s="29">
         <v>18</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="E18" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F18" s="36" t="s">
-        <v>126</v>
-      </c>
-      <c r="G18" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H18" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I18" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J18" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K18" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L18" s="13" t="str">
+      <c r="E18" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="F18" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="G18" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H18" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I18" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J18" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K18" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L18" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="M18" s="13" t="str">
+      <c r="M18" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
-      <c r="N18" s="13" t="str">
+      <c r="N18" s="11" t="str">
         <f t="shared" si="2"/>
         <v>OSM</v>
       </c>
-      <c r="O18" s="13" t="str">
+      <c r="O18" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Água.Elevatória</v>
       </c>
-      <c r="P18" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q18" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="R18" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="S18" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="T18" s="14" t="str">
+      <c r="P18" s="35" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q18" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="R18" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="S18" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T18" s="12" t="str">
         <f t="shared" si="4"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="U18" s="14" t="str">
+      <c r="U18" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Esquemas</v>
       </c>
-      <c r="V18" s="14" t="str">
+      <c r="V18" s="12" t="str">
         <f t="shared" si="6"/>
         <v>Água.Elevatória</v>
       </c>
-      <c r="W18" s="14" t="s">
+      <c r="W18" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="X18" s="30" t="str">
+      <c r="X18" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-18</v>
       </c>
-      <c r="Y18" s="61" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z18" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA18" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="AB18" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC18" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD18" s="14" t="s">
+      <c r="Y18" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z18" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA18" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="AB18" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC18" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD18" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="31">
+      <c r="A19" s="29">
         <v>19</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="E19" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F19" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="G19" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H19" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I19" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J19" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K19" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L19" s="13" t="str">
+      <c r="E19" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="F19" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="G19" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H19" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I19" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J19" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K19" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L19" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="M19" s="13" t="str">
+      <c r="M19" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
-      <c r="N19" s="13" t="str">
+      <c r="N19" s="11" t="str">
         <f t="shared" si="2"/>
         <v>OSM</v>
       </c>
-      <c r="O19" s="13" t="str">
+      <c r="O19" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Água.Torre</v>
       </c>
-      <c r="P19" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q19" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="R19" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="S19" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="T19" s="14" t="str">
+      <c r="P19" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q19" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="R19" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="S19" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T19" s="12" t="str">
         <f t="shared" si="4"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="U19" s="14" t="str">
+      <c r="U19" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Esquemas</v>
       </c>
-      <c r="V19" s="14" t="str">
+      <c r="V19" s="12" t="str">
         <f t="shared" si="6"/>
         <v>Água.Torre</v>
       </c>
-      <c r="W19" s="14" t="s">
+      <c r="W19" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="X19" s="30" t="str">
+      <c r="X19" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-19</v>
       </c>
-      <c r="Y19" s="61" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z19" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA19" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="AB19" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC19" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD19" s="14" t="s">
+      <c r="Y19" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z19" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA19" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="AB19" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC19" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD19" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="31">
+      <c r="A20" s="29">
         <v>20</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="E20" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F20" s="36" t="s">
-        <v>128</v>
-      </c>
-      <c r="G20" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H20" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I20" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J20" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K20" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L20" s="13" t="str">
+      <c r="E20" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="F20" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="G20" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H20" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I20" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J20" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K20" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L20" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="M20" s="13" t="str">
+      <c r="M20" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
-      <c r="N20" s="13" t="str">
+      <c r="N20" s="11" t="str">
         <f t="shared" si="2"/>
         <v>OSM</v>
       </c>
-      <c r="O20" s="13" t="str">
+      <c r="O20" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Água.Poço</v>
       </c>
-      <c r="P20" s="37" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q20" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="R20" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="S20" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="T20" s="14" t="str">
+      <c r="P20" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q20" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="R20" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="S20" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T20" s="12" t="str">
         <f t="shared" si="4"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="U20" s="14" t="str">
+      <c r="U20" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Esquemas</v>
       </c>
-      <c r="V20" s="14" t="str">
+      <c r="V20" s="12" t="str">
         <f t="shared" si="6"/>
         <v>Água.Poço</v>
       </c>
-      <c r="W20" s="14" t="s">
+      <c r="W20" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="X20" s="30" t="str">
+      <c r="X20" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-20</v>
       </c>
-      <c r="Y20" s="61" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z20" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA20" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="AB20" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC20" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD20" s="14" t="s">
+      <c r="Y20" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z20" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA20" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="AB20" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC20" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD20" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="31">
+      <c r="A21" s="29">
         <v>21</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="E21" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F21" s="36" t="s">
-        <v>129</v>
-      </c>
-      <c r="G21" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H21" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I21" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J21" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K21" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L21" s="13" t="str">
+      <c r="E21" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="F21" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="G21" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H21" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I21" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J21" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K21" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L21" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="M21" s="13" t="str">
+      <c r="M21" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
-      <c r="N21" s="13" t="str">
+      <c r="N21" s="11" t="str">
         <f t="shared" si="2"/>
         <v>OSM</v>
       </c>
-      <c r="O21" s="13" t="str">
+      <c r="O21" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Água.Reservatório</v>
       </c>
-      <c r="P21" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q21" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="R21" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="S21" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="T21" s="14" t="str">
+      <c r="P21" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q21" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="R21" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="S21" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T21" s="12" t="str">
         <f t="shared" si="4"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="U21" s="14" t="str">
+      <c r="U21" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Esquemas</v>
       </c>
-      <c r="V21" s="14" t="str">
+      <c r="V21" s="12" t="str">
         <f t="shared" si="6"/>
         <v>Água.Reservatório</v>
       </c>
-      <c r="W21" s="14" t="s">
+      <c r="W21" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="X21" s="30" t="str">
+      <c r="X21" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-21</v>
       </c>
-      <c r="Y21" s="61" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z21" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA21" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="AB21" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC21" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD21" s="14" t="s">
+      <c r="Y21" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z21" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA21" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="AB21" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC21" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD21" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="31">
+      <c r="A22" s="29">
         <v>22</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="E22" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F22" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="G22" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H22" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I22" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J22" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K22" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L22" s="13" t="str">
+      <c r="E22" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="F22" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="G22" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H22" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I22" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J22" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K22" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L22" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="M22" s="13" t="str">
+      <c r="M22" s="11" t="str">
         <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
-      <c r="N22" s="13" t="str">
+      <c r="N22" s="11" t="str">
         <f t="shared" si="2"/>
         <v>OSM</v>
       </c>
-      <c r="O22" s="13" t="str">
+      <c r="O22" s="11" t="str">
         <f t="shared" si="3"/>
         <v>Esgoto.Estação.de.Tratamento</v>
       </c>
-      <c r="P22" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q22" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="R22" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="S22" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="T22" s="14" t="str">
+      <c r="P22" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q22" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="R22" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="S22" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T22" s="12" t="str">
         <f t="shared" si="4"/>
         <v>Interoperabilidade</v>
       </c>
-      <c r="U22" s="14" t="str">
+      <c r="U22" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Esquemas</v>
       </c>
-      <c r="V22" s="14" t="str">
+      <c r="V22" s="12" t="str">
         <f t="shared" si="6"/>
         <v>Esgoto.Estação.de.Tratamento</v>
       </c>
-      <c r="W22" s="14" t="s">
+      <c r="W22" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="X22" s="30" t="str">
+      <c r="X22" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-22</v>
       </c>
-      <c r="Y22" s="61" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z22" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA22" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="AB22" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC22" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD22" s="14" t="s">
+      <c r="Y22" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z22" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA22" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="AB22" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC22" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD22" s="12" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="31">
+      <c r="A23" s="29">
         <v>23</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="59" t="s">
         <v>90</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="E23" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F23" s="36" t="s">
-        <v>130</v>
-      </c>
-      <c r="G23" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H23" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I23" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J23" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K23" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L23" s="13" t="str">
+      <c r="E23" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="G23" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H23" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I23" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J23" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K23" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L23" s="11" t="str">
         <f t="shared" ref="L23" si="8">CONCATENATE("", C23)</f>
         <v>Interoperabilidade</v>
       </c>
-      <c r="M23" s="13" t="str">
+      <c r="M23" s="11" t="str">
         <f t="shared" ref="M23" si="9">CONCATENATE("", D23)</f>
         <v>Esquemas</v>
       </c>
-      <c r="N23" s="13" t="str">
+      <c r="N23" s="11" t="str">
         <f t="shared" ref="N23" si="10">CONCATENATE("", E23)</f>
         <v>OSM</v>
       </c>
-      <c r="O23" s="13" t="str">
+      <c r="O23" s="11" t="str">
         <f t="shared" ref="O23" si="11">CONCATENATE("", F23)</f>
         <v>Esgoto.Elevatória</v>
       </c>
-      <c r="P23" s="37" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q23" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="R23" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="S23" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="T23" s="14" t="str">
+      <c r="P23" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q23" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="R23" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="S23" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T23" s="12" t="str">
         <f t="shared" ref="T23" si="12">SUBSTITUTE(C23, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
-      <c r="U23" s="14" t="str">
+      <c r="U23" s="12" t="str">
         <f t="shared" ref="U23" si="13">SUBSTITUTE(D23, "_", " ")</f>
         <v>Esquemas</v>
       </c>
-      <c r="V23" s="14" t="str">
+      <c r="V23" s="12" t="str">
         <f t="shared" ref="V23" si="14">SUBSTITUTE(F23, "_", " ")</f>
         <v>Esgoto.Elevatória</v>
       </c>
-      <c r="W23" s="14" t="s">
+      <c r="W23" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="X23" s="30" t="str">
-        <f t="shared" ref="X23" si="15">CONCATENATE("Key-OSMI-",A23)</f>
+      <c r="X23" s="28" t="str">
+        <f t="shared" ref="X23:X28" si="15">CONCATENATE("Key-OSMI-",A23)</f>
         <v>Key-OSMI-23</v>
       </c>
-      <c r="Y23" s="61" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z23" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA23" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="AB23" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC23" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD23" s="14" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" s="46" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="31">
+      <c r="Y23" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="Z23" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA23" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="AB23" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC23" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD23" s="12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="29">
         <v>24</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" s="60" t="s">
         <v>96</v>
       </c>
-      <c r="C24" s="43" t="s">
+      <c r="D24" s="60" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="60" t="s">
         <v>97</v>
       </c>
-      <c r="D24" s="43" t="s">
-        <v>99</v>
-      </c>
-      <c r="E24" s="43" t="s">
-        <v>98</v>
-      </c>
-      <c r="F24" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="G24" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H24" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I24" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J24" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K24" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L24" s="13" t="str">
-        <f t="shared" ref="L24:O24" si="16">SUBSTITUTE(CONCATENATE("", C24), ".", " ")</f>
+      <c r="F24" s="60" t="s">
+        <v>198</v>
+      </c>
+      <c r="G24" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H24" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I24" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J24" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K24" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L24" s="11" t="str">
+        <f t="shared" ref="L24:O28" si="16">SUBSTITUTE(CONCATENATE("", C24), ".", " ")</f>
         <v>De API</v>
       </c>
-      <c r="M24" s="13" t="str">
+      <c r="M24" s="11" t="str">
         <f t="shared" si="16"/>
         <v>Macros</v>
       </c>
-      <c r="N24" s="13" t="str">
+      <c r="N24" s="11" t="str">
         <f t="shared" si="16"/>
         <v>Métodos</v>
       </c>
-      <c r="O24" s="13" t="str">
+      <c r="O24" s="11" t="str">
         <f t="shared" si="16"/>
-        <v>API Revit</v>
-      </c>
-      <c r="P24" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q24" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="R24" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="S24" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="T24" s="14" t="str">
-        <f t="shared" ref="T24:V24" si="17">SUBSTITUTE(C24, ".", " ")</f>
+        <v>Função Auxiliar</v>
+      </c>
+      <c r="P24" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="Q24" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="R24" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="S24" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T24" s="12" t="str">
+        <f t="shared" ref="T24:V28" si="17">SUBSTITUTE(C24, ".", " ")</f>
         <v>De API</v>
       </c>
-      <c r="U24" s="14" t="str">
+      <c r="U24" s="12" t="str">
         <f t="shared" si="17"/>
         <v>Macros</v>
       </c>
-      <c r="V24" s="44" t="str">
+      <c r="V24" s="41" t="str">
         <f t="shared" si="17"/>
         <v>Métodos</v>
       </c>
-      <c r="W24" s="14" t="s">
+      <c r="W24" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="X24" s="30" t="str">
-        <f t="shared" si="7"/>
+      <c r="X24" s="28" t="str">
+        <f t="shared" si="15"/>
         <v>Key-OSMI-24</v>
       </c>
-      <c r="Y24" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z24" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA24" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB24" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC24" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD24" s="45" t="s">
+      <c r="Y24" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z24" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA24" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB24" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC24" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD24" s="12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="29">
+        <v>25</v>
+      </c>
+      <c r="B25" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" s="60" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25" s="60" t="s">
+        <v>97</v>
+      </c>
+      <c r="F25" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="G25" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H25" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I25" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J25" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K25" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L25" s="11" t="str">
+        <f t="shared" si="16"/>
+        <v>De API</v>
+      </c>
+      <c r="M25" s="11" t="str">
+        <f t="shared" si="16"/>
+        <v>Macros</v>
+      </c>
+      <c r="N25" s="11" t="str">
+        <f t="shared" si="16"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O25" s="11" t="str">
+        <f t="shared" si="16"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P25" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q25" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="R25" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="S25" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T25" s="12" t="str">
+        <f t="shared" si="17"/>
+        <v>De API</v>
+      </c>
+      <c r="U25" s="12" t="str">
+        <f t="shared" si="17"/>
+        <v>Macros</v>
+      </c>
+      <c r="V25" s="41" t="str">
+        <f t="shared" si="17"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W25" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="X25" s="28" t="str">
+        <f t="shared" si="15"/>
+        <v>Key-OSMI-25</v>
+      </c>
+      <c r="Y25" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z25" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA25" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB25" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC25" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD25" s="12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="29">
+        <v>26</v>
+      </c>
+      <c r="B26" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" s="60" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26" s="60" t="s">
+        <v>97</v>
+      </c>
+      <c r="F26" s="60" t="s">
+        <v>206</v>
+      </c>
+      <c r="G26" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H26" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I26" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J26" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K26" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L26" s="11" t="str">
+        <f t="shared" si="16"/>
+        <v>De API</v>
+      </c>
+      <c r="M26" s="11" t="str">
+        <f t="shared" si="16"/>
+        <v>Macros</v>
+      </c>
+      <c r="N26" s="11" t="str">
+        <f t="shared" si="16"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O26" s="11" t="str">
+        <f t="shared" si="16"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P26" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q26" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="R26" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="S26" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T26" s="12" t="str">
+        <f t="shared" si="17"/>
+        <v>De API</v>
+      </c>
+      <c r="U26" s="12" t="str">
+        <f t="shared" si="17"/>
+        <v>Macros</v>
+      </c>
+      <c r="V26" s="41" t="str">
+        <f t="shared" si="17"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W26" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="X26" s="28" t="str">
+        <f t="shared" si="15"/>
+        <v>Key-OSMI-26</v>
+      </c>
+      <c r="Y26" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z26" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA26" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB26" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC26" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD26" s="12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="29">
+        <v>27</v>
+      </c>
+      <c r="B27" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="C27" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" s="60" t="s">
+        <v>98</v>
+      </c>
+      <c r="E27" s="60" t="s">
+        <v>97</v>
+      </c>
+      <c r="F27" s="60" t="s">
+        <v>210</v>
+      </c>
+      <c r="G27" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H27" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I27" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J27" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K27" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L27" s="11" t="str">
+        <f t="shared" si="16"/>
+        <v>De API</v>
+      </c>
+      <c r="M27" s="11" t="str">
+        <f t="shared" si="16"/>
+        <v>Macros</v>
+      </c>
+      <c r="N27" s="11" t="str">
+        <f t="shared" si="16"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O27" s="11" t="str">
+        <f t="shared" si="16"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P27" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q27" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="R27" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="S27" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T27" s="12" t="str">
+        <f t="shared" si="17"/>
+        <v>De API</v>
+      </c>
+      <c r="U27" s="12" t="str">
+        <f t="shared" si="17"/>
+        <v>Macros</v>
+      </c>
+      <c r="V27" s="41" t="str">
+        <f t="shared" si="17"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W27" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="X27" s="28" t="str">
+        <f t="shared" si="15"/>
+        <v>Key-OSMI-27</v>
+      </c>
+      <c r="Y27" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z27" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA27" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB27" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC27" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD27" s="12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="29">
+        <v>28</v>
+      </c>
+      <c r="B28" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="D28" s="60" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="F28" s="60" t="s">
+        <v>215</v>
+      </c>
+      <c r="G28" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="H28" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I28" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J28" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K28" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="L28" s="11" t="str">
+        <f t="shared" si="16"/>
+        <v>De API</v>
+      </c>
+      <c r="M28" s="11" t="str">
+        <f t="shared" si="16"/>
+        <v>Macros</v>
+      </c>
+      <c r="N28" s="11" t="str">
+        <f t="shared" si="16"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O28" s="11" t="str">
+        <f t="shared" si="16"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P28" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q28" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="R28" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="S28" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="T28" s="12" t="str">
+        <f t="shared" si="17"/>
+        <v>De API</v>
+      </c>
+      <c r="U28" s="12" t="str">
+        <f t="shared" si="17"/>
+        <v>Macros</v>
+      </c>
+      <c r="V28" s="41" t="str">
+        <f t="shared" si="17"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W28" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="X28" s="28" t="str">
+        <f t="shared" si="15"/>
+        <v>Key-OSMI-28</v>
+      </c>
+      <c r="Y28" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z28" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA28" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB28" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC28" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD28" s="12" t="s">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B24">
-    <cfRule type="cellIs" dxfId="23" priority="3" operator="equal">
+  <conditionalFormatting sqref="A2:B28">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E28:F28">
+    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F23 F29:F1048576">
+    <cfRule type="duplicateValues" dxfId="22" priority="5"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1:F23">
-    <cfRule type="duplicateValues" dxfId="22" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="84"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F24">
-    <cfRule type="duplicateValues" dxfId="20" priority="4"/>
+  <conditionalFormatting sqref="F24:F27">
+    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="19" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC1:AD1">
-    <cfRule type="cellIs" dxfId="18" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4591,139 +5049,139 @@
   <dimension ref="A1:U2"/>
   <sheetFormatPr defaultColWidth="13.1640625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" style="22" customWidth="1"/>
-    <col min="2" max="10" width="7.6640625" style="23" customWidth="1"/>
-    <col min="11" max="21" width="7.6640625" style="21" customWidth="1"/>
-    <col min="22" max="16384" width="13.1640625" style="21"/>
+    <col min="1" max="1" width="3.33203125" style="20" customWidth="1"/>
+    <col min="2" max="10" width="7.6640625" style="21" customWidth="1"/>
+    <col min="11" max="21" width="7.6640625" style="19" customWidth="1"/>
+    <col min="22" max="16384" width="13.1640625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="18" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:21" s="16" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="M1" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="N1" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O1" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="P1" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="Q1" s="16" t="s">
+      <c r="Q1" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="R1" s="16" t="s">
+      <c r="R1" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="S1" s="16" t="s">
+      <c r="S1" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="T1" s="16" t="s">
+      <c r="T1" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="U1" s="17" t="s">
+      <c r="U1" s="15" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="19">
-        <v>2</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="I2" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="J2" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="K2" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="L2" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="M2" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="N2" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="O2" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="P2" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q2" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="R2" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="S2" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="T2" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="U2" s="20" t="s">
+    <row r="2" spans="1:21" s="16" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="17">
+        <v>2</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="M2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="N2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="O2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="R2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="S2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="T2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="U2" s="18" t="s">
         <v>2</v>
       </c>
     </row>
@@ -4746,32 +5204,32 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="27" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7" style="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="12.83203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.33203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="12.83203125" style="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24">
+      <c r="A1" s="22">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="24" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4779,22 +5237,22 @@
       <c r="A2" s="10">
         <v>2</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" s="14" t="s">
+      <c r="B2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="12" t="s">
         <v>2</v>
       </c>
     </row>
@@ -4828,152 +5286,152 @@
   <dimension ref="A1:W2"/>
   <sheetFormatPr defaultColWidth="6.1640625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" style="40" bestFit="1" customWidth="1"/>
-    <col min="4" max="23" width="5.6640625" style="40" customWidth="1"/>
-    <col min="24" max="16384" width="6.1640625" style="40"/>
+    <col min="1" max="1" width="2.5" style="39" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5" style="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" style="38" bestFit="1" customWidth="1"/>
+    <col min="4" max="23" width="5.6640625" style="38" customWidth="1"/>
+    <col min="24" max="16384" width="6.1640625" style="38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="39" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="56">
+    <row r="1" spans="1:23" s="37" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="53">
         <v>1</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="58" t="s">
+      <c r="C1" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="58" t="s">
+      <c r="D1" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="59" t="s">
+      <c r="E1" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="58" t="s">
+      <c r="F1" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="59" t="s">
+      <c r="G1" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="58" t="s">
+      <c r="H1" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="59" t="s">
+      <c r="I1" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="58" t="s">
+      <c r="J1" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="59" t="s">
+      <c r="K1" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="58" t="s">
+      <c r="L1" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="59" t="s">
+      <c r="M1" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="58" t="s">
+      <c r="N1" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="59" t="s">
+      <c r="O1" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="58" t="s">
+      <c r="P1" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="Q1" s="59" t="s">
+      <c r="Q1" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="58" t="s">
+      <c r="R1" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="S1" s="59" t="s">
+      <c r="S1" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="58" t="s">
+      <c r="T1" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="U1" s="59" t="s">
+      <c r="U1" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="V1" s="58" t="s">
+      <c r="V1" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="W1" s="60" t="s">
+      <c r="W1" s="57" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="48">
-        <v>2</v>
-      </c>
-      <c r="B2" s="49" t="s">
-        <v>109</v>
-      </c>
-      <c r="C2" s="50" t="s">
-        <v>110</v>
-      </c>
-      <c r="D2" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="52" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" s="52" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="I2" s="52" t="s">
-        <v>2</v>
-      </c>
-      <c r="J2" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="K2" s="52" t="s">
-        <v>2</v>
-      </c>
-      <c r="L2" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="M2" s="52" t="s">
-        <v>2</v>
-      </c>
-      <c r="N2" s="53" t="s">
-        <v>2</v>
-      </c>
-      <c r="O2" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="P2" s="53" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q2" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="R2" s="53" t="s">
-        <v>2</v>
-      </c>
-      <c r="S2" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="T2" s="55" t="s">
-        <v>2</v>
-      </c>
-      <c r="U2" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="V2" s="53" t="s">
-        <v>2</v>
-      </c>
-      <c r="W2" s="54" t="s">
+      <c r="A2" s="45">
+        <v>2</v>
+      </c>
+      <c r="B2" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="47" t="s">
+        <v>107</v>
+      </c>
+      <c r="D2" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="49" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="49" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="49" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="49" t="s">
+        <v>2</v>
+      </c>
+      <c r="L2" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="M2" s="49" t="s">
+        <v>2</v>
+      </c>
+      <c r="N2" s="50" t="s">
+        <v>2</v>
+      </c>
+      <c r="O2" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="50" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="R2" s="50" t="s">
+        <v>2</v>
+      </c>
+      <c r="S2" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="T2" s="52" t="s">
+        <v>2</v>
+      </c>
+      <c r="U2" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="V2" s="50" t="s">
+        <v>2</v>
+      </c>
+      <c r="W2" s="51" t="s">
         <v>2</v>
       </c>
     </row>

--- a/Versão5/GIS/Ontologia_OSM.xlsx
+++ b/Versão5/GIS/Ontologia_OSM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\GIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7F91D4-770A-4D90-BEAC-C11AC5F0C801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECDFD59-564D-437A-8CE2-33980DED9F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="681" activeTab="1" xr2:uid="{EADD6BF3-7ABC-4ACF-B5B1-0F5DE0265229}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="681" xr2:uid="{EADD6BF3-7ABC-4ACF-B5B1-0F5DE0265229}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="16" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="269">
   <si>
     <t>Organização</t>
   </si>
@@ -114,34 +114,13 @@
     <t>Escola Politécnica da UFRJ</t>
   </si>
   <si>
-    <t>NormaNúmero</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>Edição</t>
-  </si>
-  <si>
-    <t>ISBN</t>
-  </si>
-  <si>
-    <t>NormaEscopo</t>
-  </si>
-  <si>
-    <t>NormaReferência1</t>
-  </si>
-  <si>
-    <t>NormaReferência2</t>
-  </si>
-  <si>
     <t>Observações</t>
   </si>
   <si>
     <t>DataHora</t>
-  </si>
-  <si>
-    <t>Advertência1</t>
   </si>
   <si>
     <t>Algumas traduções podem precisar de revisão - Traducción al español incorporada</t>
@@ -344,9 +323,6 @@
     <t>0-CategoriaEquivalente</t>
   </si>
   <si>
-    <t>Link do Esquema</t>
-  </si>
-  <si>
     <t>Conceitos</t>
   </si>
   <si>
@@ -360,18 +336,6 @@
   </si>
   <si>
     <t>Interop</t>
-  </si>
-  <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>De.API</t>
-  </si>
-  <si>
-    <t>Métodos</t>
-  </si>
-  <si>
-    <t>Macros</t>
   </si>
   <si>
     <t>OSM</t>
@@ -720,9 +684,6 @@
     <t>Define a Function to filter objects in an application</t>
   </si>
   <si>
-    <t>Códigos.Visuais</t>
-  </si>
-  <si>
     <t>Bloco.de.Código</t>
   </si>
   <si>
@@ -736,6 +697,192 @@
   </si>
   <si>
     <t>KML</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>API.Plataforma</t>
+  </si>
+  <si>
+    <t>API.Macros</t>
+  </si>
+  <si>
+    <t>API.Método</t>
+  </si>
+  <si>
+    <t>API.Macros.Visuais</t>
+  </si>
+  <si>
+    <t>API.Método.Visual</t>
+  </si>
+  <si>
+    <t>Norma-Número</t>
+  </si>
+  <si>
+    <t>Norma-Edição</t>
+  </si>
+  <si>
+    <t>Norma-ISBN</t>
+  </si>
+  <si>
+    <t>Norma-Escopo</t>
+  </si>
+  <si>
+    <t>Norma-Referência-01</t>
+  </si>
+  <si>
+    <t>Norma-Referência-02</t>
+  </si>
+  <si>
+    <t>Norma-Referência-03</t>
+  </si>
+  <si>
+    <t>Advertência</t>
+  </si>
+  <si>
+    <t>Aviso</t>
+  </si>
+  <si>
+    <t>Alert</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-01</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-02</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-04</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-01</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-02</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-03</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-04</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-05</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-06</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-07</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-08</t>
+  </si>
+  <si>
+    <t>Fonte-SINAPI</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-01</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-02</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-04</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-01</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-02</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-03</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-04</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-05</t>
+  </si>
+  <si>
+    <t>Fonte-Bombeiros-01</t>
+  </si>
+  <si>
+    <t>https://brasil.un.org/pt-br/sdgs</t>
+  </si>
+  <si>
+    <t>https://eaesp.fgv.br/centros/centro-estudos-sustentabilidade/projetos/programa-brasileiro-ghg-protocol</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/acesso-a-informacao/acoes-e-programas/transformacao-ecologica/transformacao-ecologica</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/orgaos/spe/taxonomia-sustentavel-brasileira/cadernos</t>
+  </si>
+  <si>
+    <t>https://museunacional.ufrj.br/hortobotanico</t>
+  </si>
+  <si>
+    <t>https://www.embrapa.br/florestas/publicacoes</t>
+  </si>
+  <si>
+    <t>https://www.arvoresgigantes.org</t>
+  </si>
+  <si>
+    <t>https://www.scielo.br/j/abb</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/inpa/pt-br/Pesquisa/colecoes/botanica</t>
+  </si>
+  <si>
+    <t>https://botanicasaopaulo.org</t>
+  </si>
+  <si>
+    <t>https://pesquisa.in.gov.br/imprensa</t>
+  </si>
+  <si>
+    <t>https://mapas.florestal.gov.br</t>
+  </si>
+  <si>
+    <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
+  </si>
+  <si>
+    <t>https://somasus.saude.gov.br/sistema/home</t>
+  </si>
+  <si>
+    <t>https://anvisalegis.datalegis.net</t>
+  </si>
+  <si>
+    <t>RDC 611/2022. Radiologia diagnóstica. Blindagem, proteção radiológica.</t>
+  </si>
+  <si>
+    <t>RDC 222/2018. Gerenciamento de resíduos. Plano de gerenciamento obrigatório.</t>
+  </si>
+  <si>
+    <t>NBR 9050. Acessibilidade. Todos os ambientes de uso público.</t>
+  </si>
+  <si>
+    <t>NBR 7256. Climatização em EAS. Obrigatória para CC, CTI, CME, hemodinâmica.</t>
+  </si>
+  <si>
+    <t>NBR 15575. Desempenho de edificações. Conforto térmico, acústico, lumínico.</t>
+  </si>
+  <si>
+    <t>NBR 13534. Instalações elétricas em EAS. Circuitos, aterramento, emergência.</t>
+  </si>
+  <si>
+    <t>NBR 12188. Gases medicinais. Centrais, redes, pontos de uso.</t>
+  </si>
+  <si>
+    <t>Segurança contra incêndio. Varia por estado, consultar regulamento local.</t>
   </si>
 </sst>
 </file>
@@ -834,7 +981,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -979,6 +1126,12 @@
         <bgColor rgb="FFFEF2CB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -1112,7 +1265,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1236,9 +1389,6 @@
     <xf numFmtId="0" fontId="7" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1292,6 +1442,39 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1902,15 +2085,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{643CFCF6-0637-46A8-9CC0-1BF6FB3A6D15}">
   <sheetPr codeName="Planilha14"/>
-  <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:C49"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.5" customWidth="1"/>
+    <col min="1" max="1" width="15.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="65.33203125" style="27" customWidth="1"/>
     <col min="3" max="3" width="4.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1921,7 +2104,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -1932,18 +2115,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
@@ -1954,7 +2137,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>15</v>
       </c>
@@ -1966,7 +2149,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>16</v>
       </c>
@@ -1978,7 +2161,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>17</v>
       </c>
@@ -1989,7 +2172,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>19</v>
       </c>
@@ -2000,7 +2183,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>0</v>
       </c>
@@ -2011,177 +2194,459 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>24</v>
+        <v>214</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>25</v>
+        <v>215</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>26</v>
+        <v>216</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>27</v>
+        <v>217</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>28</v>
+        <v>218</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B16" s="44" t="s">
-        <v>103</v>
+        <v>219</v>
+      </c>
+      <c r="B16" s="43" t="s">
+        <v>91</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B18" s="7">
         <f ca="1">NOW()</f>
-        <v>46268.697977662036</v>
+        <v>46276.435401620372</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>31</v>
+        <v>220</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
-        <v>33</v>
+    <row r="20" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
+        <v>221</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
-        <v>34</v>
+    <row r="21" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
+        <v>222</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>105</v>
+        <v>26</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="8" t="str">
-        <f>_xlfn.TRANSLATE(B22,"pt","es")</f>
+        <v>27</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="8" t="str">
+        <f>_xlfn.TRANSLATE(B24,"pt","es")</f>
         <v>Formalizar los elementos del proyecto BIM en formato OSM</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="8" t="str">
-        <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
+      <c r="C25" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="8" t="str">
+        <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize BIM project elements in OSM format</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>39</v>
+      <c r="C26" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B27" s="65" t="s">
+        <v>246</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B28" s="66" t="s">
+        <v>247</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="B29" s="66" t="s">
+        <v>248</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="B30" s="67" t="s">
+        <v>249</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B31" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B32" s="68" t="s">
+        <v>251</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="B33" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B34" s="69" t="s">
+        <v>253</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="B35" s="69" t="s">
+        <v>254</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B36" s="68" t="s">
+        <v>255</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="B37" s="69" t="s">
+        <v>256</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="B38" s="68" t="s">
+        <v>257</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="B39" s="70" t="s">
+        <v>258</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="B40" s="70" t="s">
+        <v>259</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>260</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B42" s="71" t="s">
+        <v>261</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="B43" s="71" t="s">
+        <v>262</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B44" s="71" t="s">
+        <v>263</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B45" s="71" t="s">
+        <v>264</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="B46" s="71" t="s">
+        <v>265</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B47" s="71" t="s">
+        <v>266</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="B48" s="71" t="s">
+        <v>267</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="B49" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B16" r:id="rId1" xr:uid="{85F79A7A-4111-4BD8-A3C5-4FD730DA4627}"/>
+    <hyperlink ref="B27" r:id="rId2" xr:uid="{73074517-7065-4F0C-A1C9-D2FB2A1175B3}"/>
+    <hyperlink ref="B29" r:id="rId3" xr:uid="{211B2FB3-83FA-4432-BDA2-F63EF96E347E}"/>
+    <hyperlink ref="B28" r:id="rId4" xr:uid="{639A6B28-05F0-4972-BD69-71CC45F95540}"/>
+    <hyperlink ref="B39" r:id="rId5" location="categoria_888" xr:uid="{7543E5E0-E405-4FE7-9D3A-EF2A2C9007A5}"/>
+    <hyperlink ref="B40" r:id="rId6" xr:uid="{AABAE240-E4BD-4F5D-966C-4BACF4FCB1EA}"/>
+    <hyperlink ref="B41" r:id="rId7" xr:uid="{77DA490E-0B49-4036-AD60-73A14A05379F}"/>
+    <hyperlink ref="B30" r:id="rId8" xr:uid="{959C0C8C-923F-4D61-91C7-5346148AD0CC}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -2196,7 +2661,7 @@
     <col min="2" max="2" width="6.5" customWidth="1"/>
     <col min="3" max="3" width="10.6640625" customWidth="1"/>
     <col min="4" max="4" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5" customWidth="1"/>
     <col min="6" max="6" width="22.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="11" width="7.83203125" customWidth="1"/>
     <col min="12" max="12" width="12.1640625" bestFit="1" customWidth="1"/>
@@ -2205,16 +2670,16 @@
     <col min="16" max="16" width="51.83203125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="58.5" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="41.83203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.5" style="64" customWidth="1"/>
     <col min="20" max="20" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="7.1640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10" customWidth="1"/>
     <col min="24" max="24" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="59.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="64.33203125" customWidth="1"/>
     <col min="26" max="26" width="9" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="20" customWidth="1"/>
-    <col min="28" max="28" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="17.33203125" customWidth="1"/>
+    <col min="28" max="28" width="7" customWidth="1"/>
     <col min="29" max="29" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
@@ -2224,111 +2689,111 @@
         <v>1</v>
       </c>
       <c r="B1" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="K1" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="L1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="M1" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="32" t="s">
-        <v>101</v>
-      </c>
-      <c r="G1" s="33" t="s">
+      <c r="N1" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="33" t="s">
+      <c r="O1" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="P1" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="33" t="s">
+      <c r="Q1" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="K1" s="33" t="s">
+      <c r="R1" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="S1" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="T1" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="U1" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="V1" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="W1" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="X1" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="Y1" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Z1" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA1" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="R1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="S1" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="T1" s="9" t="s">
+      <c r="AB1" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC1" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="U1" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="V1" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="W1" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="X1" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y1" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="Z1" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="AA1" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB1" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC1" s="9" t="s">
-        <v>62</v>
-      </c>
       <c r="AD1" s="9" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="29">
         <v>2</v>
       </c>
-      <c r="B2" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C2" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="E2" s="59" t="s">
-        <v>99</v>
+      <c r="B2" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="58" t="s">
+        <v>87</v>
       </c>
       <c r="F2" s="34" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="G2" s="30" t="s">
         <v>2</v>
@@ -2362,15 +2827,15 @@
         <v>Energia.Gerador</v>
       </c>
       <c r="P2" s="35" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="Q2" s="12" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="R2" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="S2" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="S2" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T2" s="12" t="str">
@@ -2386,20 +2851,20 @@
         <v>Energia.Gerador</v>
       </c>
       <c r="W2" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X2" s="28" t="str">
         <f>CONCATENATE("Key-OSMI-",A2)</f>
         <v>Key-OSMI-2</v>
       </c>
-      <c r="Y2" s="58" t="s">
-        <v>128</v>
+      <c r="Y2" s="57" t="s">
+        <v>116</v>
       </c>
       <c r="Z2" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AA2" s="58" t="s">
-        <v>129</v>
+      <c r="AA2" s="57" t="s">
+        <v>117</v>
       </c>
       <c r="AB2" s="12" t="s">
         <v>2</v>
@@ -2415,20 +2880,20 @@
       <c r="A3" s="29">
         <v>3</v>
       </c>
-      <c r="B3" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="E3" s="59" t="s">
-        <v>99</v>
+      <c r="B3" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="58" t="s">
+        <v>87</v>
       </c>
       <c r="F3" s="34" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="G3" s="30" t="s">
         <v>2</v>
@@ -2462,15 +2927,15 @@
         <v>Energia.Usina</v>
       </c>
       <c r="P3" s="35" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="Q3" s="12" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="R3" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="S3" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="S3" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T3" s="12" t="str">
@@ -2486,20 +2951,20 @@
         <v>Energia.Usina</v>
       </c>
       <c r="W3" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X3" s="28" t="str">
         <f t="shared" ref="X3:X22" si="7">CONCATENATE("Key-OSMI-",A3)</f>
         <v>Key-OSMI-3</v>
       </c>
-      <c r="Y3" s="58" t="s">
-        <v>128</v>
+      <c r="Y3" s="57" t="s">
+        <v>116</v>
       </c>
       <c r="Z3" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AA3" s="58" t="s">
-        <v>129</v>
+      <c r="AA3" s="57" t="s">
+        <v>117</v>
       </c>
       <c r="AB3" s="12" t="s">
         <v>2</v>
@@ -2515,20 +2980,20 @@
       <c r="A4" s="29">
         <v>4</v>
       </c>
-      <c r="B4" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C4" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" s="59" t="s">
-        <v>99</v>
+      <c r="B4" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="58" t="s">
+        <v>87</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="G4" s="30" t="s">
         <v>2</v>
@@ -2562,15 +3027,15 @@
         <v>Energia.Linha</v>
       </c>
       <c r="P4" s="35" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="R4" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="S4" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="S4" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T4" s="12" t="str">
@@ -2586,20 +3051,20 @@
         <v>Energia.Linha</v>
       </c>
       <c r="W4" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X4" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-4</v>
       </c>
-      <c r="Y4" s="58" t="s">
-        <v>128</v>
+      <c r="Y4" s="57" t="s">
+        <v>116</v>
       </c>
       <c r="Z4" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AA4" s="58" t="s">
-        <v>129</v>
+      <c r="AA4" s="57" t="s">
+        <v>117</v>
       </c>
       <c r="AB4" s="12" t="s">
         <v>2</v>
@@ -2615,20 +3080,20 @@
       <c r="A5" s="29">
         <v>5</v>
       </c>
-      <c r="B5" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5" s="59" t="s">
-        <v>99</v>
+      <c r="B5" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="58" t="s">
+        <v>87</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="G5" s="30" t="s">
         <v>2</v>
@@ -2662,15 +3127,15 @@
         <v>Energia.Subestação</v>
       </c>
       <c r="P5" s="35" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="Q5" s="12" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="R5" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="S5" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="S5" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T5" s="12" t="str">
@@ -2686,20 +3151,20 @@
         <v>Energia.Subestação</v>
       </c>
       <c r="W5" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X5" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-5</v>
       </c>
-      <c r="Y5" s="58" t="s">
-        <v>128</v>
+      <c r="Y5" s="57" t="s">
+        <v>116</v>
       </c>
       <c r="Z5" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AA5" s="58" t="s">
-        <v>129</v>
+      <c r="AA5" s="57" t="s">
+        <v>117</v>
       </c>
       <c r="AB5" s="12" t="s">
         <v>2</v>
@@ -2715,20 +3180,20 @@
       <c r="A6" s="29">
         <v>6</v>
       </c>
-      <c r="B6" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="E6" s="59" t="s">
+      <c r="B6" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="58" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="34" t="s">
         <v>99</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>111</v>
       </c>
       <c r="G6" s="30" t="s">
         <v>2</v>
@@ -2762,15 +3227,15 @@
         <v>Energia.Transformador</v>
       </c>
       <c r="P6" s="35" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="Q6" s="12" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="R6" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="S6" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="S6" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T6" s="12" t="str">
@@ -2786,20 +3251,20 @@
         <v>Energia.Transformador</v>
       </c>
       <c r="W6" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X6" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-6</v>
       </c>
-      <c r="Y6" s="58" t="s">
-        <v>128</v>
+      <c r="Y6" s="57" t="s">
+        <v>116</v>
       </c>
       <c r="Z6" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AA6" s="58" t="s">
-        <v>129</v>
+      <c r="AA6" s="57" t="s">
+        <v>117</v>
       </c>
       <c r="AB6" s="12" t="s">
         <v>2</v>
@@ -2815,20 +3280,20 @@
       <c r="A7" s="29">
         <v>7</v>
       </c>
-      <c r="B7" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7" s="59" t="s">
-        <v>99</v>
+      <c r="B7" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" s="58" t="s">
+        <v>87</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="G7" s="30" t="s">
         <v>2</v>
@@ -2862,15 +3327,15 @@
         <v>Energia.Interruptor</v>
       </c>
       <c r="P7" s="35" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="R7" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="S7" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="S7" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T7" s="12" t="str">
@@ -2886,20 +3351,20 @@
         <v>Energia.Interruptor</v>
       </c>
       <c r="W7" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X7" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-7</v>
       </c>
-      <c r="Y7" s="58" t="s">
-        <v>128</v>
+      <c r="Y7" s="57" t="s">
+        <v>116</v>
       </c>
       <c r="Z7" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AA7" s="58" t="s">
-        <v>129</v>
+      <c r="AA7" s="57" t="s">
+        <v>117</v>
       </c>
       <c r="AB7" s="12" t="s">
         <v>2</v>
@@ -2915,20 +3380,20 @@
       <c r="A8" s="29">
         <v>8</v>
       </c>
-      <c r="B8" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="E8" s="59" t="s">
-        <v>99</v>
+      <c r="B8" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="58" t="s">
+        <v>87</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="G8" s="30" t="s">
         <v>2</v>
@@ -2962,15 +3427,15 @@
         <v>Energia.Compensador</v>
       </c>
       <c r="P8" s="35" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="R8" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="S8" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="S8" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T8" s="12" t="str">
@@ -2986,20 +3451,20 @@
         <v>Energia.Compensador</v>
       </c>
       <c r="W8" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X8" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-8</v>
       </c>
-      <c r="Y8" s="58" t="s">
-        <v>128</v>
+      <c r="Y8" s="57" t="s">
+        <v>116</v>
       </c>
       <c r="Z8" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AA8" s="58" t="s">
-        <v>129</v>
+      <c r="AA8" s="57" t="s">
+        <v>117</v>
       </c>
       <c r="AB8" s="12" t="s">
         <v>2</v>
@@ -3015,20 +3480,20 @@
       <c r="A9" s="29">
         <v>9</v>
       </c>
-      <c r="B9" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="E9" s="59" t="s">
-        <v>99</v>
+      <c r="B9" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="58" t="s">
+        <v>87</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="G9" s="30" t="s">
         <v>2</v>
@@ -3062,15 +3527,15 @@
         <v>Energia.Torre</v>
       </c>
       <c r="P9" s="35" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="Q9" s="12" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="R9" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="S9" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="S9" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T9" s="12" t="str">
@@ -3086,20 +3551,20 @@
         <v>Energia.Torre</v>
       </c>
       <c r="W9" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X9" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-9</v>
       </c>
-      <c r="Y9" s="58" t="s">
-        <v>128</v>
+      <c r="Y9" s="57" t="s">
+        <v>116</v>
       </c>
       <c r="Z9" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AA9" s="58" t="s">
-        <v>129</v>
+      <c r="AA9" s="57" t="s">
+        <v>117</v>
       </c>
       <c r="AB9" s="12" t="s">
         <v>2</v>
@@ -3115,20 +3580,20 @@
       <c r="A10" s="29">
         <v>10</v>
       </c>
-      <c r="B10" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" s="59" t="s">
-        <v>99</v>
+      <c r="B10" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="58" t="s">
+        <v>87</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="G10" s="30" t="s">
         <v>2</v>
@@ -3162,15 +3627,15 @@
         <v>Telecom.Edifício</v>
       </c>
       <c r="P10" s="35" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="R10" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="S10" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="S10" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T10" s="12" t="str">
@@ -3186,20 +3651,20 @@
         <v>Telecom.Edifício</v>
       </c>
       <c r="W10" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X10" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-10</v>
       </c>
-      <c r="Y10" s="58" t="s">
-        <v>128</v>
+      <c r="Y10" s="57" t="s">
+        <v>116</v>
       </c>
       <c r="Z10" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="AA10" s="58" t="s">
-        <v>129</v>
+      <c r="AA10" s="57" t="s">
+        <v>117</v>
       </c>
       <c r="AB10" s="12" t="s">
         <v>2</v>
@@ -3215,20 +3680,20 @@
       <c r="A11" s="29">
         <v>11</v>
       </c>
-      <c r="B11" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C11" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="E11" s="59" t="s">
-        <v>99</v>
+      <c r="B11" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="58" t="s">
+        <v>87</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="G11" s="30" t="s">
         <v>2</v>
@@ -3262,15 +3727,15 @@
         <v>Telecom.Cabo</v>
       </c>
       <c r="P11" s="35" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="Q11" s="12" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="R11" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="S11" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="S11" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T11" s="12" t="str">
@@ -3286,20 +3751,20 @@
         <v>Telecom.Cabo</v>
       </c>
       <c r="W11" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X11" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-11</v>
       </c>
-      <c r="Y11" s="58" t="s">
-        <v>128</v>
+      <c r="Y11" s="57" t="s">
+        <v>116</v>
       </c>
       <c r="Z11" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="AA11" s="58" t="s">
-        <v>129</v>
+      <c r="AA11" s="57" t="s">
+        <v>117</v>
       </c>
       <c r="AB11" s="12" t="s">
         <v>2</v>
@@ -3315,20 +3780,20 @@
       <c r="A12" s="29">
         <v>12</v>
       </c>
-      <c r="B12" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C12" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="E12" s="59" t="s">
-        <v>99</v>
+      <c r="B12" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" s="58" t="s">
+        <v>87</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="G12" s="30" t="s">
         <v>2</v>
@@ -3362,15 +3827,15 @@
         <v>Telecom.Mastro</v>
       </c>
       <c r="P12" s="35" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="Q12" s="12" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="R12" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="S12" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="S12" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T12" s="12" t="str">
@@ -3386,20 +3851,20 @@
         <v>Telecom.Mastro</v>
       </c>
       <c r="W12" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X12" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-12</v>
       </c>
-      <c r="Y12" s="58" t="s">
-        <v>128</v>
+      <c r="Y12" s="57" t="s">
+        <v>116</v>
       </c>
       <c r="Z12" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="AA12" s="58" t="s">
-        <v>129</v>
+      <c r="AA12" s="57" t="s">
+        <v>117</v>
       </c>
       <c r="AB12" s="12" t="s">
         <v>2</v>
@@ -3415,20 +3880,20 @@
       <c r="A13" s="29">
         <v>13</v>
       </c>
-      <c r="B13" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C13" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="E13" s="59" t="s">
-        <v>99</v>
+      <c r="B13" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="58" t="s">
+        <v>87</v>
       </c>
       <c r="F13" s="34" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G13" s="30" t="s">
         <v>2</v>
@@ -3462,15 +3927,15 @@
         <v>Oleoduto</v>
       </c>
       <c r="P13" s="35" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="Q13" s="12" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="R13" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="S13" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="S13" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T13" s="12" t="str">
@@ -3486,20 +3951,20 @@
         <v>Oleoduto</v>
       </c>
       <c r="W13" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X13" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-13</v>
       </c>
-      <c r="Y13" s="58" t="s">
-        <v>130</v>
+      <c r="Y13" s="57" t="s">
+        <v>118</v>
       </c>
       <c r="Z13" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AA13" s="58" t="s">
-        <v>131</v>
+      <c r="AA13" s="57" t="s">
+        <v>119</v>
       </c>
       <c r="AB13" s="12" t="s">
         <v>2</v>
@@ -3515,20 +3980,20 @@
       <c r="A14" s="29">
         <v>14</v>
       </c>
-      <c r="B14" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C14" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="E14" s="59" t="s">
-        <v>99</v>
+      <c r="B14" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="58" t="s">
+        <v>87</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="G14" s="30" t="s">
         <v>2</v>
@@ -3562,15 +4027,15 @@
         <v>Oleoduto.Parte.de.Tubulação</v>
       </c>
       <c r="P14" s="35" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="Q14" s="12" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="R14" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="S14" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="S14" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T14" s="12" t="str">
@@ -3586,20 +4051,20 @@
         <v>Oleoduto.Parte.de.Tubulação</v>
       </c>
       <c r="W14" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X14" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-14</v>
       </c>
-      <c r="Y14" s="58" t="s">
-        <v>130</v>
+      <c r="Y14" s="57" t="s">
+        <v>118</v>
       </c>
       <c r="Z14" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AA14" s="58" t="s">
-        <v>131</v>
+      <c r="AA14" s="57" t="s">
+        <v>119</v>
       </c>
       <c r="AB14" s="12" t="s">
         <v>2</v>
@@ -3615,20 +4080,20 @@
       <c r="A15" s="29">
         <v>15</v>
       </c>
-      <c r="B15" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="E15" s="59" t="s">
-        <v>99</v>
+      <c r="B15" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" s="58" t="s">
+        <v>87</v>
       </c>
       <c r="F15" s="34" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="G15" s="30" t="s">
         <v>2</v>
@@ -3662,15 +4127,15 @@
         <v>Petróleo.Campo</v>
       </c>
       <c r="P15" s="35" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="Q15" s="12" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="R15" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="S15" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="S15" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T15" s="12" t="str">
@@ -3686,20 +4151,20 @@
         <v>Petróleo.Campo</v>
       </c>
       <c r="W15" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X15" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-15</v>
       </c>
-      <c r="Y15" s="58" t="s">
-        <v>130</v>
+      <c r="Y15" s="57" t="s">
+        <v>118</v>
       </c>
       <c r="Z15" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AA15" s="58" t="s">
-        <v>131</v>
+      <c r="AA15" s="57" t="s">
+        <v>119</v>
       </c>
       <c r="AB15" s="12" t="s">
         <v>2</v>
@@ -3715,20 +4180,20 @@
       <c r="A16" s="29">
         <v>16</v>
       </c>
-      <c r="B16" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="E16" s="59" t="s">
-        <v>99</v>
+      <c r="B16" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" s="58" t="s">
+        <v>87</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="G16" s="30" t="s">
         <v>2</v>
@@ -3762,15 +4227,15 @@
         <v>Petróleo.Poço</v>
       </c>
       <c r="P16" s="35" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="Q16" s="12" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="R16" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="S16" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="S16" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T16" s="12" t="str">
@@ -3786,20 +4251,20 @@
         <v>Petróleo.Poço</v>
       </c>
       <c r="W16" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X16" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-16</v>
       </c>
-      <c r="Y16" s="58" t="s">
-        <v>130</v>
+      <c r="Y16" s="57" t="s">
+        <v>118</v>
       </c>
       <c r="Z16" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AA16" s="58" t="s">
-        <v>131</v>
+      <c r="AA16" s="57" t="s">
+        <v>119</v>
       </c>
       <c r="AB16" s="12" t="s">
         <v>2</v>
@@ -3815,20 +4280,20 @@
       <c r="A17" s="29">
         <v>17</v>
       </c>
-      <c r="B17" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="E17" s="59" t="s">
-        <v>99</v>
+      <c r="B17" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="58" t="s">
+        <v>87</v>
       </c>
       <c r="F17" s="34" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="G17" s="30" t="s">
         <v>2</v>
@@ -3862,15 +4327,15 @@
         <v>Água.Estação.de.Tratamento</v>
       </c>
       <c r="P17" s="35" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="Q17" s="12" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="R17" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="S17" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="S17" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T17" s="12" t="str">
@@ -3886,20 +4351,20 @@
         <v>Água.Estação.de.Tratamento</v>
       </c>
       <c r="W17" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X17" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-17</v>
       </c>
-      <c r="Y17" s="58" t="s">
-        <v>130</v>
+      <c r="Y17" s="57" t="s">
+        <v>118</v>
       </c>
       <c r="Z17" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AA17" s="58" t="s">
-        <v>131</v>
+      <c r="AA17" s="57" t="s">
+        <v>119</v>
       </c>
       <c r="AB17" s="12" t="s">
         <v>2</v>
@@ -3915,20 +4380,20 @@
       <c r="A18" s="29">
         <v>18</v>
       </c>
-      <c r="B18" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D18" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="E18" s="59" t="s">
-        <v>99</v>
+      <c r="B18" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" s="58" t="s">
+        <v>87</v>
       </c>
       <c r="F18" s="34" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="G18" s="30" t="s">
         <v>2</v>
@@ -3962,15 +4427,15 @@
         <v>Água.Elevatória</v>
       </c>
       <c r="P18" s="35" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="Q18" s="12" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="R18" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="S18" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="S18" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T18" s="12" t="str">
@@ -3986,20 +4451,20 @@
         <v>Água.Elevatória</v>
       </c>
       <c r="W18" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X18" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-18</v>
       </c>
-      <c r="Y18" s="58" t="s">
-        <v>130</v>
+      <c r="Y18" s="57" t="s">
+        <v>118</v>
       </c>
       <c r="Z18" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AA18" s="58" t="s">
-        <v>131</v>
+      <c r="AA18" s="57" t="s">
+        <v>119</v>
       </c>
       <c r="AB18" s="12" t="s">
         <v>2</v>
@@ -4015,20 +4480,20 @@
       <c r="A19" s="29">
         <v>19</v>
       </c>
-      <c r="B19" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C19" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="E19" s="59" t="s">
-        <v>99</v>
+      <c r="B19" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" s="58" t="s">
+        <v>87</v>
       </c>
       <c r="F19" s="34" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="G19" s="30" t="s">
         <v>2</v>
@@ -4062,15 +4527,15 @@
         <v>Água.Torre</v>
       </c>
       <c r="P19" s="35" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="Q19" s="12" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="R19" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="S19" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="S19" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T19" s="12" t="str">
@@ -4086,20 +4551,20 @@
         <v>Água.Torre</v>
       </c>
       <c r="W19" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X19" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-19</v>
       </c>
-      <c r="Y19" s="58" t="s">
-        <v>130</v>
+      <c r="Y19" s="57" t="s">
+        <v>118</v>
       </c>
       <c r="Z19" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AA19" s="58" t="s">
-        <v>131</v>
+      <c r="AA19" s="57" t="s">
+        <v>119</v>
       </c>
       <c r="AB19" s="12" t="s">
         <v>2</v>
@@ -4115,20 +4580,20 @@
       <c r="A20" s="29">
         <v>20</v>
       </c>
-      <c r="B20" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="E20" s="59" t="s">
-        <v>99</v>
+      <c r="B20" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="58" t="s">
+        <v>87</v>
       </c>
       <c r="F20" s="34" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="G20" s="30" t="s">
         <v>2</v>
@@ -4162,15 +4627,15 @@
         <v>Água.Poço</v>
       </c>
       <c r="P20" s="35" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="R20" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="S20" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="S20" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T20" s="12" t="str">
@@ -4186,20 +4651,20 @@
         <v>Água.Poço</v>
       </c>
       <c r="W20" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X20" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-20</v>
       </c>
-      <c r="Y20" s="58" t="s">
-        <v>130</v>
+      <c r="Y20" s="57" t="s">
+        <v>118</v>
       </c>
       <c r="Z20" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AA20" s="58" t="s">
-        <v>131</v>
+      <c r="AA20" s="57" t="s">
+        <v>119</v>
       </c>
       <c r="AB20" s="12" t="s">
         <v>2</v>
@@ -4215,20 +4680,20 @@
       <c r="A21" s="29">
         <v>21</v>
       </c>
-      <c r="B21" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="E21" s="59" t="s">
-        <v>99</v>
+      <c r="B21" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" s="58" t="s">
+        <v>87</v>
       </c>
       <c r="F21" s="34" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="G21" s="30" t="s">
         <v>2</v>
@@ -4262,15 +4727,15 @@
         <v>Água.Reservatório</v>
       </c>
       <c r="P21" s="35" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="Q21" s="12" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="R21" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="S21" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="S21" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T21" s="12" t="str">
@@ -4286,20 +4751,20 @@
         <v>Água.Reservatório</v>
       </c>
       <c r="W21" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X21" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-21</v>
       </c>
-      <c r="Y21" s="58" t="s">
-        <v>130</v>
+      <c r="Y21" s="57" t="s">
+        <v>118</v>
       </c>
       <c r="Z21" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AA21" s="58" t="s">
-        <v>131</v>
+      <c r="AA21" s="57" t="s">
+        <v>119</v>
       </c>
       <c r="AB21" s="12" t="s">
         <v>2</v>
@@ -4315,20 +4780,20 @@
       <c r="A22" s="29">
         <v>22</v>
       </c>
-      <c r="B22" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C22" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D22" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="E22" s="59" t="s">
-        <v>99</v>
+      <c r="B22" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" s="58" t="s">
+        <v>87</v>
       </c>
       <c r="F22" s="34" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="G22" s="30" t="s">
         <v>2</v>
@@ -4362,15 +4827,15 @@
         <v>Esgoto.Estação.de.Tratamento</v>
       </c>
       <c r="P22" s="35" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="Q22" s="12" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="R22" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="S22" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="S22" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T22" s="12" t="str">
@@ -4386,20 +4851,20 @@
         <v>Esgoto.Estação.de.Tratamento</v>
       </c>
       <c r="W22" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X22" s="28" t="str">
         <f t="shared" si="7"/>
         <v>Key-OSMI-22</v>
       </c>
-      <c r="Y22" s="58" t="s">
-        <v>130</v>
+      <c r="Y22" s="57" t="s">
+        <v>118</v>
       </c>
       <c r="Z22" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AA22" s="58" t="s">
-        <v>131</v>
+      <c r="AA22" s="57" t="s">
+        <v>119</v>
       </c>
       <c r="AB22" s="12" t="s">
         <v>2</v>
@@ -4415,20 +4880,20 @@
       <c r="A23" s="29">
         <v>23</v>
       </c>
-      <c r="B23" s="59" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" s="59" t="s">
-        <v>91</v>
-      </c>
-      <c r="E23" s="59" t="s">
-        <v>99</v>
+      <c r="B23" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" s="60" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="58" t="s">
+        <v>87</v>
       </c>
       <c r="F23" s="34" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="G23" s="30" t="s">
         <v>2</v>
@@ -4446,7 +4911,7 @@
         <v>2</v>
       </c>
       <c r="L23" s="11" t="str">
-        <f t="shared" ref="L23" si="8">CONCATENATE("", C23)</f>
+        <f t="shared" ref="L23:M28" si="8">CONCATENATE("", C23)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M23" s="11" t="str">
@@ -4462,15 +4927,15 @@
         <v>Esgoto.Elevatória</v>
       </c>
       <c r="P23" s="35" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="Q23" s="12" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="R23" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="S23" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="S23" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T23" s="12" t="str">
@@ -4486,20 +4951,20 @@
         <v>Esgoto.Elevatória</v>
       </c>
       <c r="W23" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X23" s="28" t="str">
-        <f t="shared" ref="X23:X28" si="15">CONCATENATE("Key-OSMI-",A23)</f>
+        <f t="shared" ref="X23" si="15">CONCATENATE("Key-OSMI-",A23)</f>
         <v>Key-OSMI-23</v>
       </c>
-      <c r="Y23" s="58" t="s">
-        <v>130</v>
+      <c r="Y23" s="57" t="s">
+        <v>118</v>
       </c>
       <c r="Z23" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AA23" s="58" t="s">
-        <v>131</v>
+      <c r="AA23" s="57" t="s">
+        <v>119</v>
       </c>
       <c r="AB23" s="12" t="s">
         <v>2</v>
@@ -4511,24 +4976,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:30" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="29">
         <v>24</v>
       </c>
-      <c r="B24" s="59" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24" s="60" t="s">
-        <v>98</v>
-      </c>
-      <c r="E24" s="60" t="s">
-        <v>97</v>
-      </c>
-      <c r="F24" s="60" t="s">
-        <v>198</v>
+      <c r="B24" s="58" t="s">
+        <v>207</v>
+      </c>
+      <c r="C24" s="59" t="s">
+        <v>208</v>
+      </c>
+      <c r="D24" s="59" t="s">
+        <v>209</v>
+      </c>
+      <c r="E24" s="59" t="s">
+        <v>210</v>
+      </c>
+      <c r="F24" s="59" t="s">
+        <v>186</v>
       </c>
       <c r="G24" s="30" t="s">
         <v>2</v>
@@ -4546,50 +5011,50 @@
         <v>2</v>
       </c>
       <c r="L24" s="11" t="str">
-        <f t="shared" ref="L24:O28" si="16">SUBSTITUTE(CONCATENATE("", C24), ".", " ")</f>
-        <v>De API</v>
+        <f t="shared" si="8"/>
+        <v>API.Plataforma</v>
       </c>
       <c r="M24" s="11" t="str">
-        <f t="shared" si="16"/>
-        <v>Macros</v>
+        <f t="shared" si="8"/>
+        <v>API.Macros</v>
       </c>
       <c r="N24" s="11" t="str">
-        <f t="shared" si="16"/>
-        <v>Métodos</v>
+        <f t="shared" ref="N24:O28" si="16">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E24),"."," ")," De "," de "))</f>
+        <v>API Método</v>
       </c>
       <c r="O24" s="11" t="str">
         <f t="shared" si="16"/>
         <v>Função Auxiliar</v>
       </c>
       <c r="P24" s="12" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="R24" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="S24" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="S24" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T24" s="12" t="str">
         <f t="shared" ref="T24:V28" si="17">SUBSTITUTE(C24, ".", " ")</f>
-        <v>De API</v>
+        <v>API Plataforma</v>
       </c>
       <c r="U24" s="12" t="str">
         <f t="shared" si="17"/>
-        <v>Macros</v>
+        <v>API Macros</v>
       </c>
       <c r="V24" s="41" t="str">
         <f t="shared" si="17"/>
-        <v>Métodos</v>
+        <v>API Método</v>
       </c>
       <c r="W24" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X24" s="28" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="X24:X28" si="18">CONCATENATE("Key-OSMI-",A24)</f>
         <v>Key-OSMI-24</v>
       </c>
       <c r="Y24" s="42" t="s">
@@ -4607,28 +5072,28 @@
       <c r="AC24" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AD24" s="12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:30" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD24" s="42" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="29">
         <v>25</v>
       </c>
-      <c r="B25" s="59" t="s">
-        <v>95</v>
-      </c>
-      <c r="C25" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="D25" s="60" t="s">
-        <v>98</v>
-      </c>
-      <c r="E25" s="60" t="s">
-        <v>97</v>
-      </c>
-      <c r="F25" s="60" t="s">
-        <v>202</v>
+      <c r="B25" s="58" t="s">
+        <v>207</v>
+      </c>
+      <c r="C25" s="59" t="s">
+        <v>208</v>
+      </c>
+      <c r="D25" s="59" t="s">
+        <v>209</v>
+      </c>
+      <c r="E25" s="59" t="s">
+        <v>210</v>
+      </c>
+      <c r="F25" s="59" t="s">
+        <v>190</v>
       </c>
       <c r="G25" s="30" t="s">
         <v>2</v>
@@ -4646,50 +5111,50 @@
         <v>2</v>
       </c>
       <c r="L25" s="11" t="str">
-        <f t="shared" si="16"/>
-        <v>De API</v>
+        <f t="shared" si="8"/>
+        <v>API.Plataforma</v>
       </c>
       <c r="M25" s="11" t="str">
-        <f t="shared" si="16"/>
-        <v>Macros</v>
+        <f t="shared" si="8"/>
+        <v>API.Macros</v>
       </c>
       <c r="N25" s="11" t="str">
         <f t="shared" si="16"/>
-        <v>Métodos</v>
+        <v>API Método</v>
       </c>
       <c r="O25" s="11" t="str">
         <f t="shared" si="16"/>
         <v>Função Global</v>
       </c>
       <c r="P25" s="12" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="Q25" s="12" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="R25" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="S25" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="S25" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T25" s="12" t="str">
         <f t="shared" si="17"/>
-        <v>De API</v>
+        <v>API Plataforma</v>
       </c>
       <c r="U25" s="12" t="str">
         <f t="shared" si="17"/>
-        <v>Macros</v>
+        <v>API Macros</v>
       </c>
       <c r="V25" s="41" t="str">
         <f t="shared" si="17"/>
-        <v>Métodos</v>
+        <v>API Método</v>
       </c>
       <c r="W25" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X25" s="28" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>Key-OSMI-25</v>
       </c>
       <c r="Y25" s="42" t="s">
@@ -4707,28 +5172,28 @@
       <c r="AC25" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AD25" s="12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD25" s="42" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="29">
         <v>26</v>
       </c>
-      <c r="B26" s="59" t="s">
-        <v>95</v>
-      </c>
-      <c r="C26" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="D26" s="60" t="s">
-        <v>98</v>
-      </c>
-      <c r="E26" s="60" t="s">
-        <v>97</v>
-      </c>
-      <c r="F26" s="60" t="s">
-        <v>206</v>
+      <c r="B26" s="58" t="s">
+        <v>207</v>
+      </c>
+      <c r="C26" s="59" t="s">
+        <v>208</v>
+      </c>
+      <c r="D26" s="59" t="s">
+        <v>209</v>
+      </c>
+      <c r="E26" s="59" t="s">
+        <v>210</v>
+      </c>
+      <c r="F26" s="59" t="s">
+        <v>194</v>
       </c>
       <c r="G26" s="30" t="s">
         <v>2</v>
@@ -4746,50 +5211,50 @@
         <v>2</v>
       </c>
       <c r="L26" s="11" t="str">
-        <f t="shared" si="16"/>
-        <v>De API</v>
+        <f t="shared" si="8"/>
+        <v>API.Plataforma</v>
       </c>
       <c r="M26" s="11" t="str">
-        <f t="shared" si="16"/>
-        <v>Macros</v>
+        <f t="shared" si="8"/>
+        <v>API.Macros</v>
       </c>
       <c r="N26" s="11" t="str">
         <f t="shared" si="16"/>
-        <v>Métodos</v>
+        <v>API Método</v>
       </c>
       <c r="O26" s="11" t="str">
         <f t="shared" si="16"/>
         <v>Função Local</v>
       </c>
       <c r="P26" s="12" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="Q26" s="12" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="R26" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="S26" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="S26" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T26" s="12" t="str">
         <f t="shared" si="17"/>
-        <v>De API</v>
+        <v>API Plataforma</v>
       </c>
       <c r="U26" s="12" t="str">
         <f t="shared" si="17"/>
-        <v>Macros</v>
+        <v>API Macros</v>
       </c>
       <c r="V26" s="41" t="str">
         <f t="shared" si="17"/>
-        <v>Métodos</v>
+        <v>API Método</v>
       </c>
       <c r="W26" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X26" s="28" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>Key-OSMI-26</v>
       </c>
       <c r="Y26" s="42" t="s">
@@ -4807,29 +5272,29 @@
       <c r="AC26" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AD26" s="12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD26" s="42" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="29">
         <v>27</v>
       </c>
-      <c r="B27" s="59" t="s">
-        <v>95</v>
-      </c>
-      <c r="C27" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="D27" s="60" t="s">
-        <v>98</v>
-      </c>
-      <c r="E27" s="60" t="s">
-        <v>97</v>
-      </c>
-      <c r="F27" s="60" t="s">
+      <c r="B27" s="58" t="s">
+        <v>207</v>
+      </c>
+      <c r="C27" s="59" t="s">
+        <v>208</v>
+      </c>
+      <c r="D27" s="59" t="s">
+        <v>209</v>
+      </c>
+      <c r="E27" s="59" t="s">
         <v>210</v>
       </c>
+      <c r="F27" s="59" t="s">
+        <v>198</v>
+      </c>
       <c r="G27" s="30" t="s">
         <v>2</v>
       </c>
@@ -4846,50 +5311,50 @@
         <v>2</v>
       </c>
       <c r="L27" s="11" t="str">
-        <f t="shared" si="16"/>
-        <v>De API</v>
+        <f t="shared" si="8"/>
+        <v>API.Plataforma</v>
       </c>
       <c r="M27" s="11" t="str">
-        <f t="shared" si="16"/>
-        <v>Macros</v>
+        <f t="shared" si="8"/>
+        <v>API.Macros</v>
       </c>
       <c r="N27" s="11" t="str">
         <f t="shared" si="16"/>
-        <v>Métodos</v>
+        <v>API Método</v>
       </c>
       <c r="O27" s="11" t="str">
         <f t="shared" si="16"/>
         <v>Função Filtro</v>
       </c>
       <c r="P27" s="12" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="Q27" s="12" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="R27" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="S27" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="S27" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T27" s="12" t="str">
         <f t="shared" si="17"/>
-        <v>De API</v>
+        <v>API Plataforma</v>
       </c>
       <c r="U27" s="12" t="str">
         <f t="shared" si="17"/>
-        <v>Macros</v>
+        <v>API Macros</v>
       </c>
       <c r="V27" s="41" t="str">
         <f t="shared" si="17"/>
-        <v>Métodos</v>
+        <v>API Método</v>
       </c>
       <c r="W27" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X27" s="28" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>Key-OSMI-27</v>
       </c>
       <c r="Y27" s="42" t="s">
@@ -4907,28 +5372,28 @@
       <c r="AC27" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AD27" s="12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:30" s="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD27" s="42" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="29">
         <v>28</v>
       </c>
-      <c r="B28" s="59" t="s">
-        <v>95</v>
-      </c>
-      <c r="C28" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="D28" s="60" t="s">
-        <v>98</v>
-      </c>
-      <c r="E28" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="F28" s="60" t="s">
-        <v>215</v>
+      <c r="B28" s="58" t="s">
+        <v>207</v>
+      </c>
+      <c r="C28" s="59" t="s">
+        <v>208</v>
+      </c>
+      <c r="D28" s="59" t="s">
+        <v>211</v>
+      </c>
+      <c r="E28" s="59" t="s">
+        <v>212</v>
+      </c>
+      <c r="F28" s="59" t="s">
+        <v>202</v>
       </c>
       <c r="G28" s="30" t="s">
         <v>2</v>
@@ -4946,50 +5411,50 @@
         <v>2</v>
       </c>
       <c r="L28" s="11" t="str">
-        <f t="shared" si="16"/>
-        <v>De API</v>
+        <f t="shared" si="8"/>
+        <v>API.Plataforma</v>
       </c>
       <c r="M28" s="11" t="str">
-        <f t="shared" si="16"/>
-        <v>Macros</v>
+        <f t="shared" si="8"/>
+        <v>API.Macros.Visuais</v>
       </c>
       <c r="N28" s="11" t="str">
         <f t="shared" si="16"/>
-        <v>Códigos Visuais</v>
+        <v>API Método Visual</v>
       </c>
       <c r="O28" s="11" t="str">
         <f t="shared" si="16"/>
         <v>Bloco de Código</v>
       </c>
       <c r="P28" s="12" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="R28" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="S28" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="S28" s="61" t="s">
         <v>2</v>
       </c>
       <c r="T28" s="12" t="str">
         <f t="shared" si="17"/>
-        <v>De API</v>
+        <v>API Plataforma</v>
       </c>
       <c r="U28" s="12" t="str">
         <f t="shared" si="17"/>
-        <v>Macros</v>
+        <v>API Macros Visuais</v>
       </c>
       <c r="V28" s="41" t="str">
         <f t="shared" si="17"/>
-        <v>Códigos Visuais</v>
+        <v>API Método Visual</v>
       </c>
       <c r="W28" s="12" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="X28" s="28" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>Key-OSMI-28</v>
       </c>
       <c r="Y28" s="42" t="s">
@@ -5007,35 +5472,33 @@
       <c r="AC28" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="AD28" s="12" t="s">
+      <c r="AD28" s="42" t="s">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B28">
-    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
+  <conditionalFormatting sqref="A2:B23 A24:A28">
+    <cfRule type="cellIs" dxfId="24" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E28:F28">
-    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F1:F23 F29:F1048576">
-    <cfRule type="duplicateValues" dxfId="22" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F23">
-    <cfRule type="duplicateValues" dxfId="21" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="87"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24:F27">
-    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
+  <conditionalFormatting sqref="F24:F28">
+    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="19" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC1:AD1">
-    <cfRule type="cellIs" dxfId="18" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5057,67 +5520,67 @@
   <sheetData>
     <row r="1" spans="1:21" s="16" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="J1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="K1" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="L1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="M1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="N1" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="O1" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="P1" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="Q1" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="R1" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="S1" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="T1" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="U1" s="15" t="s">
         <v>78</v>
-      </c>
-      <c r="O1" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="P1" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q1" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="R1" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="S1" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="T1" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="U1" s="15" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:21" s="16" customFormat="1" x14ac:dyDescent="0.15">
@@ -5215,22 +5678,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E1" s="24" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5284,154 +5747,154 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB5F366C-5F74-4E71-97A7-7194C8A394D8}">
   <dimension ref="A1:W2"/>
-  <sheetFormatPr defaultColWidth="6.1640625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.5" style="39" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5" style="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" style="38" bestFit="1" customWidth="1"/>
-    <col min="4" max="23" width="5.6640625" style="38" customWidth="1"/>
-    <col min="24" max="16384" width="6.1640625" style="38"/>
+    <col min="2" max="2" width="7" style="36" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" style="38" customWidth="1"/>
+    <col min="4" max="23" width="4.83203125" style="38" customWidth="1"/>
+    <col min="24" max="16384" width="9" style="38"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" s="37" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="53">
+      <c r="A1" s="52">
         <v>1</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="55" t="s">
+      <c r="C1" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="55" t="s">
+      <c r="D1" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="55" t="s">
+      <c r="F1" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="56" t="s">
+      <c r="G1" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="55" t="s">
+      <c r="H1" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="56" t="s">
+      <c r="I1" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="55" t="s">
+      <c r="J1" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="56" t="s">
+      <c r="K1" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="55" t="s">
+      <c r="L1" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="56" t="s">
+      <c r="M1" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="55" t="s">
+      <c r="N1" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="56" t="s">
+      <c r="O1" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="55" t="s">
+      <c r="P1" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="Q1" s="56" t="s">
+      <c r="Q1" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="55" t="s">
+      <c r="R1" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="S1" s="56" t="s">
+      <c r="S1" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="55" t="s">
+      <c r="T1" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="U1" s="56" t="s">
+      <c r="U1" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="V1" s="55" t="s">
+      <c r="V1" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="W1" s="57" t="s">
+      <c r="W1" s="56" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="45">
-        <v>2</v>
-      </c>
-      <c r="B2" s="46" t="s">
-        <v>106</v>
-      </c>
-      <c r="C2" s="47" t="s">
-        <v>107</v>
-      </c>
-      <c r="D2" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="49" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" s="49" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="I2" s="49" t="s">
-        <v>2</v>
-      </c>
-      <c r="J2" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="K2" s="49" t="s">
-        <v>2</v>
-      </c>
-      <c r="L2" s="48" t="s">
-        <v>2</v>
-      </c>
-      <c r="M2" s="49" t="s">
-        <v>2</v>
-      </c>
-      <c r="N2" s="50" t="s">
-        <v>2</v>
-      </c>
-      <c r="O2" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="P2" s="50" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q2" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="R2" s="50" t="s">
-        <v>2</v>
-      </c>
-      <c r="S2" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="T2" s="52" t="s">
-        <v>2</v>
-      </c>
-      <c r="U2" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="V2" s="50" t="s">
-        <v>2</v>
-      </c>
-      <c r="W2" s="51" t="s">
+      <c r="A2" s="44">
+        <v>2</v>
+      </c>
+      <c r="B2" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" s="47" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="47" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="47" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="47" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="L2" s="47" t="s">
+        <v>2</v>
+      </c>
+      <c r="M2" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="N2" s="49" t="s">
+        <v>2</v>
+      </c>
+      <c r="O2" s="50" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="49" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="50" t="s">
+        <v>2</v>
+      </c>
+      <c r="R2" s="49" t="s">
+        <v>2</v>
+      </c>
+      <c r="S2" s="50" t="s">
+        <v>2</v>
+      </c>
+      <c r="T2" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="U2" s="50" t="s">
+        <v>2</v>
+      </c>
+      <c r="V2" s="49" t="s">
+        <v>2</v>
+      </c>
+      <c r="W2" s="50" t="s">
         <v>2</v>
       </c>
     </row>
